--- a/data/대학도서관_설문대상_발송명단.xlsx
+++ b/data/대학도서관_설문대상_발송명단.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M404"/>
+  <dimension ref="A1:N404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,6 +536,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>통합도서관부호</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -550,7 +556,9 @@
           <t>가야대학교 분성도서관</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="3" t="n">
+        <v>247024</v>
+      </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -590,6 +598,11 @@
       <c r="M2" s="3" t="inlineStr">
         <is>
           <t>장애학생지원센터 통계: 없음(X)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>가야대학교 분성도서관: 248032</t>
         </is>
       </c>
     </row>
@@ -607,7 +620,9 @@
           <t>가천대학교 중앙도서관; 가천대학교 중앙도서관(M)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="3" t="n">
+        <v>241005</v>
+      </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -647,6 +662,11 @@
       <c r="M3" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 가천의과학대학교+가천길대학(일반+전문)('06), 경원대학교+경원전문대학(일반+전문)('07), 가천의과학대학교+경원대학교(일반+일반)('12) / 대학도서관 통계 2개 캠퍼스 통합: 가천대학교 중앙도서관; 가천대학교 중앙도서관(M) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 10명</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>가천대학교 중앙도서관(M): 코드 미확인</t>
         </is>
       </c>
     </row>
@@ -664,7 +684,9 @@
           <t>가톨릭관동대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="3" t="n">
+        <v>242003</v>
+      </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -706,6 +728,7 @@
           <t>[교육부고시 비고] 구)관동대학교('14 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 18명</t>
         </is>
       </c>
+      <c r="N4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -721,7 +744,9 @@
           <t>가톨릭꽃동네대학교 도서관</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="3" t="n">
+        <v>243019</v>
+      </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -763,6 +788,7 @@
           <t>[교육부고시 비고] 구)꽃동네대학교('21.5.15 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 2명</t>
         </is>
       </c>
+      <c r="N5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -778,7 +804,9 @@
           <t>가톨릭대학교 성신교정도서관; 가톨릭대학교 성심교정도서관; 가톨릭대학교 성의교정도서관</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="3" t="n">
+        <v>241027</v>
+      </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -818,6 +846,11 @@
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 3개 캠퍼스 통합: 가톨릭대학교 성신교정도서관; 가톨릭대학교 성심교정도서관; 가톨릭대학교 성의교정도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 3개 통합집계) · 장애재학생수(학부) 합계 36명</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>가톨릭대학교 성신교정 도서관: 211001; 가톨릭대학교 성의교정 도서관: 211002</t>
         </is>
       </c>
     </row>
@@ -835,7 +868,9 @@
           <t>감리교신학대학교 도서관</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="D7" s="3" t="n">
+        <v>211003</v>
+      </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -877,6 +912,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 9명</t>
         </is>
       </c>
+      <c r="N7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -892,7 +928,9 @@
           <t>강남대학교 도서관</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="3" t="n">
+        <v>241001</v>
+      </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -934,6 +972,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 84명</t>
         </is>
       </c>
+      <c r="N8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -949,7 +988,9 @@
           <t>강원대학교 도서관; 강원대학교 삼척도서관; 국립강릉원주대학교 도서관 원주분관; 국립강릉원주대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="D9" s="3" t="n">
+        <v>242002</v>
+      </c>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -989,6 +1030,11 @@
       <c r="M9" s="3" t="inlineStr">
         <is>
           <t>통폐합: 구 '국립강릉원주대학교' → 2026.3. 강원대학교와 통합('통합 강원대') / [교육부고시 비고] 강원대학교+삼척대학교(일반+산업)('06), 강원대학교+국립강릉원주대학교(일반+일반)('26) / 대학도서관 통계 4개 캠퍼스 통합: 강원대학교 도서관; 강원대학교 삼척도서관; 국립강릉원주대학교 도서관 원주분관; 국립강릉원주대학교 중앙도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 4개 통합집계) · 장애재학생수(학부) 합계 104명</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>강원대학교 삼척도서관: 242006; 강원대학교 원주캠퍼스 도서관: 242011; 강원대학교 강릉캠퍼스 도서관: 242001</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1052,9 @@
           <t>건국대학교 상허기념도서관</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="3" t="n">
+        <v>211004</v>
+      </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1048,6 +1096,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 128명</t>
         </is>
       </c>
+      <c r="N10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1063,7 +1112,9 @@
           <t>건국대학교(글로컬) 중원도서관</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="D11" s="3" t="n">
+        <v>243001</v>
+      </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1105,6 +1156,7 @@
           <t>교육부 고시상 본교와 별도의 독립 학교(분교)로 등재 - 도서관 통계도 별도 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 12명</t>
         </is>
       </c>
+      <c r="N11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1120,7 +1172,9 @@
           <t>건양대학교 대전캠퍼스 의학도서관; 건양대학교 도서관</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="3" t="n">
+        <v>244001</v>
+      </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1160,6 +1214,11 @@
       <c r="M12" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 건양대학교 대전캠퍼스 의학도서관; 건양대학교 도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 5명</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>건양대학교 대전캠퍼스 의학도서관: 230006</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1236,9 @@
           <t>경기대학교 금화도서관; 경기대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr"/>
+      <c r="D13" s="3" t="n">
+        <v>241002</v>
+      </c>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1217,6 +1278,11 @@
       <c r="M13" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 경기대학교 금화도서관; 경기대학교 중앙도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 12명</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>경기대학교 금화도서관: 211005</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1300,9 @@
           <t>경남대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="D14" s="3" t="n">
+        <v>248002</v>
+      </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1276,6 +1344,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 22명</t>
         </is>
       </c>
+      <c r="N14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1291,7 +1360,9 @@
           <t>경동대학교 도서관</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr"/>
+      <c r="D15" s="3" t="n">
+        <v>242019</v>
+      </c>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1333,6 +1404,7 @@
           <t>[교육부고시 비고] 경동대학교+동우대학(일반+전문)('13) / 장애학생지원센터 통계: 있음(O) (캠퍼스 3개 통합집계) · 장애재학생수(학부) 합계 1명</t>
         </is>
       </c>
+      <c r="N15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1348,7 +1420,9 @@
           <t>경북대학교 도서관</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="D16" s="3" t="n">
+        <v>222001</v>
+      </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1390,6 +1464,7 @@
           <t>[교육부고시 비고] 경북대학교+상주대학교(일반+산업)('08) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 91명</t>
         </is>
       </c>
+      <c r="N16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1405,7 +1480,9 @@
           <t>경상국립대학교 도서관</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="D17" s="3" t="n">
+        <v>248003</v>
+      </c>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1447,6 +1524,7 @@
           <t>[교육부고시 비고] 경상대학교(명칭 변경)+경남과학기술대학교(일반+일반)('21) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 34명</t>
         </is>
       </c>
+      <c r="N17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1462,7 +1540,9 @@
           <t>경성대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>221002</v>
+      </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1504,6 +1584,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 11명</t>
         </is>
       </c>
+      <c r="N18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1519,7 +1600,9 @@
           <t>경운대학교 벽강중앙도서관</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="D19" s="3" t="n">
+        <v>247036</v>
+      </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1561,6 +1644,7 @@
           <t>[교육부고시 비고] 산업→일반('12) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 9명</t>
         </is>
       </c>
+      <c r="N19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1576,7 +1660,9 @@
           <t>경일대학교 도서관</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>222002</v>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1618,6 +1704,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 3명</t>
         </is>
       </c>
+      <c r="N20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1633,7 +1720,9 @@
           <t>서라벌대학교 학술정보원; 신경주대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="D21" s="3" t="n">
+        <v>247022</v>
+      </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1673,6 +1762,11 @@
       <c r="M21" s="3" t="inlineStr">
         <is>
           <t>통폐합: 구 '서라벌대학교' → 2024.3. 경주대학교와 통합, 신경주대학교로 개편 / [교육부고시 비고] 경주대학교+서라벌대학교(일반+전문)('24 변경) / 대학도서관 통계 2개 캠퍼스 통합: 서라벌대학교 학술정보원; 신경주대학교 학술정보원 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 10명</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>서라벌대학교 학술정보원: 247005</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1784,9 @@
           <t>경희대학교 국제캠퍼스 중앙도서관; 경희대학교 도서관</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
+      <c r="D22" s="3" t="n">
+        <v>211006</v>
+      </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1730,6 +1826,11 @@
       <c r="M22" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 본분교 통합('12) / 대학도서관 통계 2개 캠퍼스 통합: 경희대학교 국제캠퍼스 중앙도서관; 경희대학교 도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 77명</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>경희대학교 국제캠퍼스 중앙도서관: 241008</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1848,9 @@
           <t>계명대학교 동산도서관; 계명대학교 의학도서관</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr"/>
+      <c r="D23" s="3" t="n">
+        <v>222003</v>
+      </c>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1787,6 +1890,11 @@
       <c r="M23" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 계명대학교 동산도서관; 계명대학교 의학도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 29명</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>계명대학교 의학도서관: 222004</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1912,9 @@
           <t>고려대학교 도서관</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
+      <c r="D24" s="3" t="n">
+        <v>211009</v>
+      </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1846,6 +1956,7 @@
           <t>[교육부고시 비고] 고려대학교+고려대학교병설보건대학(일반+전문)('06) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 188명</t>
         </is>
       </c>
+      <c r="N24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1861,7 +1972,9 @@
           <t>고려대학교(세종) 세종캠퍼스 학술정보원</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>244002</v>
+      </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1903,6 +2016,7 @@
           <t>교육부 고시상 본교와 별도의 독립 학교(분교)로 등재 - 도서관 통계도 별도 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 18명</t>
         </is>
       </c>
+      <c r="N25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1918,7 +2032,9 @@
           <t>고신대학교 도서관</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="D26" s="3" t="n">
+        <v>221003</v>
+      </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1960,6 +2076,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 23명</t>
         </is>
       </c>
+      <c r="N26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1975,7 +2092,9 @@
           <t>국립공주대학교 도서관</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr"/>
+      <c r="D27" s="3" t="n">
+        <v>244004</v>
+      </c>
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -2017,6 +2136,7 @@
           <t>[교육부고시 비고] 공주대학교+천안공대(일반+전문)('05), 구)공주대학교('24 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 43명</t>
         </is>
       </c>
+      <c r="N27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2032,7 +2152,9 @@
           <t>광신대학교 도서관</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="D28" s="3" t="n">
+        <v>224016</v>
+      </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2074,6 +2196,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2089,7 +2212,9 @@
           <t>광운대학교 도서관</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr"/>
+      <c r="D29" s="3" t="n">
+        <v>211012</v>
+      </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2131,6 +2256,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 3명</t>
         </is>
       </c>
+      <c r="N29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2146,7 +2272,9 @@
           <t>광주가톨릭대학교 도서관</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr"/>
+      <c r="D30" s="3" t="n">
+        <v>224001</v>
+      </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2188,6 +2316,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2203,7 +2332,9 @@
           <t>광주과학기술원 도서관</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr"/>
+      <c r="D31" s="3" t="n">
+        <v>324015</v>
+      </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2245,6 +2376,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2260,7 +2392,9 @@
           <t>광주대학교 호심기념도서관</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="D32" s="3" t="n">
+        <v>224003</v>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2302,6 +2436,7 @@
           <t>[교육부고시 비고] 산업→일반('04) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 4명</t>
         </is>
       </c>
+      <c r="N32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2317,7 +2452,9 @@
           <t>광주여자대학교 도서관</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr"/>
+      <c r="D33" s="3" t="n">
+        <v>224005</v>
+      </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2359,6 +2496,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 5명</t>
         </is>
       </c>
+      <c r="N33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2374,7 +2512,9 @@
           <t>국민대학교 성곡도서관</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr"/>
+      <c r="D34" s="3" t="n">
+        <v>211014</v>
+      </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2416,6 +2556,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 4명</t>
         </is>
       </c>
+      <c r="N34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2431,7 +2572,9 @@
           <t>국립군산대학교 도서관</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr"/>
+      <c r="D35" s="3" t="n">
+        <v>245002</v>
+      </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2473,6 +2616,7 @@
           <t>[교육부고시 비고] 구)군산대학교('24 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 14명</t>
         </is>
       </c>
+      <c r="N35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2488,7 +2632,9 @@
           <t>극동대학교 도서관</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr"/>
+      <c r="D36" s="3" t="n">
+        <v>243017</v>
+      </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2530,6 +2676,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2545,7 +2692,9 @@
           <t>금강대학교 원각도서관</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr"/>
+      <c r="D37" s="3" t="n">
+        <v>244033</v>
+      </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2587,6 +2736,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2602,7 +2752,9 @@
           <t>국립금오공과대학교 도서관</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="D38" s="3" t="n">
+        <v>247006</v>
+      </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2644,6 +2796,7 @@
           <t>[교육부고시 비고] 구)금오공과대학교('24 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 9명</t>
         </is>
       </c>
+      <c r="N38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2659,7 +2812,9 @@
           <t>김천대학교 도서관</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr"/>
+      <c r="D39" s="3" t="n">
+        <v>247008</v>
+      </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2701,6 +2856,7 @@
           <t>[교육부고시 비고] 전문→일반('10) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 0명</t>
         </is>
       </c>
+      <c r="N39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2716,7 +2872,9 @@
           <t>나사렛대학교 도서관</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr"/>
+      <c r="D40" s="3" t="n">
+        <v>244014</v>
+      </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2758,6 +2916,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 227명</t>
         </is>
       </c>
+      <c r="N40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2773,7 +2932,9 @@
           <t>남부대학교 도서관</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr"/>
+      <c r="D41" s="3" t="n">
+        <v>224018</v>
+      </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2815,6 +2976,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 11명</t>
         </is>
       </c>
+      <c r="N41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2830,7 +2992,9 @@
           <t>남서울대학교 도서관</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr"/>
+      <c r="D42" s="3" t="n">
+        <v>244021</v>
+      </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2872,6 +3036,7 @@
           <t>[교육부고시 비고] 산업→일반('12) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 23명</t>
         </is>
       </c>
+      <c r="N42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2887,7 +3052,9 @@
           <t>단국대학교 율곡기념도서관; 단국대학교 퇴계기념중앙도서관</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr"/>
+      <c r="D43" s="3" t="n">
+        <v>244006</v>
+      </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2927,6 +3094,11 @@
       <c r="M43" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 본분교 통합('14) / 대학도서관 통계 2개 캠퍼스 통합: 단국대학교 율곡기념도서관; 단국대학교 퇴계기념중앙도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 105명</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>단국대학교 퇴계기념도서관: 211017</t>
         </is>
       </c>
     </row>
@@ -2944,7 +3116,9 @@
           <t>대구가톨릭대학교 루가(의학)도서관; 대구가톨릭대학교 신학도서관; 대구가톨릭대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr"/>
+      <c r="D44" s="3" t="n">
+        <v>247023</v>
+      </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2984,6 +3158,11 @@
       <c r="M44" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 3개 캠퍼스 통합: 대구가톨릭대학교 루가(의학)도서관; 대구가톨릭대학교 신학도서관; 대구가톨릭대학교 중앙도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 28명</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>대구가톨릭대학교신학도서관: 227002; 대구가톨릭대학교의학도서관: 222007</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3180,9 @@
           <t>대구경북과학기술원 학술정보관</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr"/>
+      <c r="D45" s="3" t="n">
+        <v>327005</v>
+      </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3043,6 +3224,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -3058,7 +3240,9 @@
           <t>대구대학교 도서관</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr"/>
+      <c r="D46" s="3" t="n">
+        <v>247009</v>
+      </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3100,6 +3284,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 298명</t>
         </is>
       </c>
+      <c r="N46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -3115,7 +3300,9 @@
           <t>대구예술대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr"/>
+      <c r="D47" s="3" t="n">
+        <v>247026</v>
+      </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -3157,6 +3344,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 0명</t>
         </is>
       </c>
+      <c r="N47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -3172,7 +3360,9 @@
           <t>대구한의대학교 향산도서관</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr"/>
+      <c r="D48" s="3" t="n">
+        <v>247004</v>
+      </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3214,6 +3404,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 3명</t>
         </is>
       </c>
+      <c r="N48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3229,7 +3420,9 @@
           <t>대신대학교 도서관 (경북, 경산)</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr"/>
+      <c r="D49" s="3" t="n">
+        <v>247010</v>
+      </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3271,6 +3464,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 19명</t>
         </is>
       </c>
+      <c r="N49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -3286,7 +3480,9 @@
           <t>대전가톨릭대학교 도서관</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr"/>
+      <c r="D50" s="3" t="n">
+        <v>244022</v>
+      </c>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3328,6 +3524,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3343,7 +3540,9 @@
           <t>대전대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr"/>
+      <c r="D51" s="3" t="n">
+        <v>225002</v>
+      </c>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3385,6 +3584,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 8명</t>
         </is>
       </c>
+      <c r="N51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3400,7 +3600,9 @@
           <t>대전신학대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr"/>
+      <c r="D52" s="3" t="n">
+        <v>225015</v>
+      </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3442,6 +3644,7 @@
           <t>[교육부고시 비고] 구)대전신학교(각종→일반)('09) / 장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3457,7 +3660,9 @@
           <t>대진대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr"/>
+      <c r="D53" s="3" t="n">
+        <v>241014</v>
+      </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3499,6 +3704,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 8명</t>
         </is>
       </c>
+      <c r="N53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3514,7 +3720,9 @@
           <t>덕성여자대학교 도서관</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr"/>
+      <c r="D54" s="3" t="n">
+        <v>211019</v>
+      </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3556,6 +3764,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 16명</t>
         </is>
       </c>
+      <c r="N54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3571,7 +3780,9 @@
           <t>동국대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr"/>
+      <c r="D55" s="3" t="n">
+        <v>211020</v>
+      </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3613,6 +3824,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 33명</t>
         </is>
       </c>
+      <c r="N55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3628,7 +3840,9 @@
           <t>동국대학교 WISE캠퍼스 학술정보원</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr"/>
+      <c r="D56" s="3" t="n">
+        <v>247011</v>
+      </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3670,6 +3884,7 @@
           <t>교육부 고시상 본교와 별도의 독립 학교(분교)로 등재 - 도서관 통계도 별도 / [교육부고시 비고] 경주캠퍼스→WISE캠퍼스('22.4.26) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 8명</t>
         </is>
       </c>
+      <c r="N56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3685,7 +3900,9 @@
           <t>동덕여자대학교 춘강학술정보관</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr"/>
+      <c r="D57" s="3" t="n">
+        <v>211021</v>
+      </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3727,6 +3944,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3742,7 +3960,9 @@
           <t>동명대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr"/>
+      <c r="D58" s="3" t="n">
+        <v>221030</v>
+      </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3784,6 +4004,7 @@
           <t>[교육부고시 비고] 동명정보대학교+동명대학(산업+전문)('06) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 20명</t>
         </is>
       </c>
+      <c r="N58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -3799,7 +4020,9 @@
           <t>동서대학교 민석도서관</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr"/>
+      <c r="D59" s="3" t="n">
+        <v>221007</v>
+      </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3841,6 +4064,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 9명</t>
         </is>
       </c>
+      <c r="N59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3856,7 +4080,9 @@
           <t>동신대학교 학술문화정보원</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr"/>
+      <c r="D60" s="3" t="n">
+        <v>246001</v>
+      </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3898,6 +4124,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 8명</t>
         </is>
       </c>
+      <c r="N60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -3913,7 +4140,9 @@
           <t>동아대학교 도서관</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr"/>
+      <c r="D61" s="3" t="n">
+        <v>221008</v>
+      </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3955,6 +4184,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
         </is>
       </c>
+      <c r="N61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -3970,7 +4200,9 @@
           <t>동양대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr"/>
+      <c r="D62" s="3" t="n">
+        <v>247028</v>
+      </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -4012,6 +4244,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 2명</t>
         </is>
       </c>
+      <c r="N62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -4027,7 +4260,9 @@
           <t>동의대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr"/>
+      <c r="D63" s="3" t="n">
+        <v>221010</v>
+      </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -4069,6 +4304,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 12명</t>
         </is>
       </c>
+      <c r="N63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -4084,7 +4320,9 @@
           <t>루터대학교 도서관</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr"/>
+      <c r="D64" s="3" t="n">
+        <v>241017</v>
+      </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -4126,6 +4364,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 5명</t>
         </is>
       </c>
+      <c r="N64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -4141,7 +4380,9 @@
           <t>명지대학교 도서관</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr"/>
+      <c r="D65" s="3" t="n">
+        <v>211023</v>
+      </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -4183,6 +4424,7 @@
           <t>장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 151명</t>
         </is>
       </c>
+      <c r="N65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -4198,7 +4440,9 @@
           <t>목원대학교 도서관</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr"/>
+      <c r="D66" s="3" t="n">
+        <v>225006</v>
+      </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -4240,6 +4484,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 26명</t>
         </is>
       </c>
+      <c r="N66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -4255,7 +4500,9 @@
           <t>목포가톨릭대학교 도서관</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr"/>
+      <c r="D67" s="3" t="n">
+        <v>246005</v>
+      </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -4297,6 +4544,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 2명</t>
         </is>
       </c>
+      <c r="N67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -4312,7 +4560,9 @@
           <t>국립목포대학교 도서관; 전남도립대학교 도서관</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr"/>
+      <c r="D68" s="3" t="n">
+        <v>246002</v>
+      </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4352,6 +4602,11 @@
       <c r="M68" s="3" t="inlineStr">
         <is>
           <t>통폐합: 구 '전남도립대학교' → 2026.3. 국립목포대학교와 통합(2·4년제 통합모델) / [교육부고시 비고] 구)목포대학교('24 변경), 국립목포대학교+전남도립대학교(일반+전문)('26) / 대학도서관 통계 2개 캠퍼스 통합: 국립목포대학교 도서관; 전남도립대학교 도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 23명</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>전남도립대학교도서관: 246024</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4624,9 @@
           <t>국립목포해양대학교 도서관</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr"/>
+      <c r="D69" s="3" t="n">
+        <v>246004</v>
+      </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4411,6 +4668,7 @@
           <t>[교육부고시 비고] 구)목포해양대학교('24 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 0명</t>
         </is>
       </c>
+      <c r="N69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -4426,7 +4684,9 @@
           <t>배재대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr"/>
+      <c r="D70" s="3" t="n">
+        <v>225007</v>
+      </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4468,6 +4728,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 23명</t>
         </is>
       </c>
+      <c r="N70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -4483,7 +4744,9 @@
           <t>백석대학교 도서관(서울); 백석대학교 도서관(천안)</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr"/>
+      <c r="D71" s="3" t="n">
+        <v>244020</v>
+      </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4523,6 +4786,11 @@
       <c r="M71" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 백석대학교 도서관(서울); 백석대학교 도서관(천안) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>백석대학교 서울캠퍼스학술정보관: 211074</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4808,9 @@
           <t>국립부경대학교 도서관</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr"/>
+      <c r="D72" s="3" t="n">
+        <v>221031</v>
+      </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4582,6 +4852,7 @@
           <t>[교육부고시 비고] 구)부경대학교('24 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 15명</t>
         </is>
       </c>
+      <c r="N72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -4597,7 +4868,9 @@
           <t>부산가톨릭대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr"/>
+      <c r="D73" s="3" t="n">
+        <v>221037</v>
+      </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4639,6 +4912,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 11명</t>
         </is>
       </c>
+      <c r="N73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -4654,7 +4928,9 @@
           <t>부산대학교 도서관</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr"/>
+      <c r="D74" s="3" t="n">
+        <v>221016</v>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4696,6 +4972,7 @@
           <t>[교육부고시 비고] 부산대학교+밀양대학교(일반+산업)('06) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 75명</t>
         </is>
       </c>
+      <c r="N74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -4711,7 +4988,9 @@
           <t>부산외국어대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr"/>
+      <c r="D75" s="3" t="n">
+        <v>221022</v>
+      </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4753,6 +5032,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 15명</t>
         </is>
       </c>
+      <c r="N75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -4768,7 +5048,9 @@
           <t>부산장신대학교 도서관</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr"/>
+      <c r="D76" s="3" t="n">
+        <v>221034</v>
+      </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4810,6 +5092,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 3명</t>
         </is>
       </c>
+      <c r="N76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -4825,7 +5108,9 @@
           <t>삼육대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr"/>
+      <c r="D77" s="3" t="n">
+        <v>211027</v>
+      </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4867,6 +5152,7 @@
           <t>[교육부고시 비고] 삼육대학교+삼육의명대학(일반+전문)('06) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 52명</t>
         </is>
       </c>
+      <c r="N77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -4882,7 +5168,9 @@
           <t>상명대학교 서울캠퍼스 학술정보관; 상명대학교 천안캠퍼스 학술정보관</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr"/>
+      <c r="D78" s="3" t="n">
+        <v>211028</v>
+      </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4922,6 +5210,11 @@
       <c r="M78" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 상명대학교 서울캠퍼스 학술정보관; 상명대학교 천안캠퍼스 학술정보관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 42명</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>상명대학교 천안캠퍼스 학술정보관: 244007</t>
         </is>
       </c>
     </row>
@@ -4939,7 +5232,9 @@
           <t>상지대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr"/>
+      <c r="D79" s="3" t="n">
+        <v>242007</v>
+      </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4981,6 +5276,7 @@
           <t>[교육부고시 비고] 상지대학교+상지영서대학교(일반+전문)('20) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 9명</t>
         </is>
       </c>
+      <c r="N79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -4996,7 +5292,9 @@
           <t>서강대학교 로욜라도서관</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr"/>
+      <c r="D80" s="3" t="n">
+        <v>211029</v>
+      </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -5038,6 +5336,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 35명</t>
         </is>
       </c>
+      <c r="N80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -5053,7 +5352,9 @@
           <t>서경대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr"/>
+      <c r="D81" s="3" t="n">
+        <v>211015</v>
+      </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5095,6 +5396,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -5110,7 +5412,9 @@
           <t>서울과학기술대학교 도서관</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr"/>
+      <c r="D82" s="3" t="n">
+        <v>211034</v>
+      </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -5152,6 +5456,7 @@
           <t>[교육부고시 비고] 구)서울산업대학교('10 변경), 산업→ 일반('12) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 31명</t>
         </is>
       </c>
+      <c r="N82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -5167,7 +5472,9 @@
           <t>서울기독대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr"/>
+      <c r="D83" s="3" t="n">
+        <v>211018</v>
+      </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -5209,6 +5516,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 2명</t>
         </is>
       </c>
+      <c r="N83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -5224,7 +5532,9 @@
           <t>서울대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr"/>
+      <c r="D84" s="3" t="n">
+        <v>211032</v>
+      </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -5266,6 +5576,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 54명</t>
         </is>
       </c>
+      <c r="N84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -5281,7 +5592,9 @@
           <t>서울시립대학교 도서관</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr"/>
+      <c r="D85" s="3" t="n">
+        <v>211035</v>
+      </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -5323,6 +5636,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 43명</t>
         </is>
       </c>
+      <c r="N85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -5338,7 +5652,9 @@
           <t>서울신학대학교 도서관</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr"/>
+      <c r="D86" s="3" t="n">
+        <v>241023</v>
+      </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5380,6 +5696,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 14명</t>
         </is>
       </c>
+      <c r="N86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -5395,7 +5712,9 @@
           <t>서울여자대학교 도서관</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr"/>
+      <c r="D87" s="3" t="n">
+        <v>211036</v>
+      </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5437,6 +5756,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 3명</t>
         </is>
       </c>
+      <c r="N87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -5452,7 +5772,9 @@
           <t>서울장신대학교 도서관</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr"/>
+      <c r="D88" s="3" t="n">
+        <v>241024</v>
+      </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5494,6 +5816,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
         </is>
       </c>
+      <c r="N88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -5509,7 +5832,9 @@
           <t>서울한영대학교 도서관</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr"/>
+      <c r="D89" s="3" t="n">
+        <v>211056</v>
+      </c>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5551,6 +5876,7 @@
           <t>[교육부고시 비고] 구)한영신학대학교('17 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 28명</t>
         </is>
       </c>
+      <c r="N89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -5566,7 +5892,9 @@
           <t>서원대학교 도서관</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr"/>
+      <c r="D90" s="3" t="n">
+        <v>243003</v>
+      </c>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5608,6 +5936,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
         </is>
       </c>
+      <c r="N90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -5623,7 +5952,9 @@
           <t>선문대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr"/>
+      <c r="D91" s="3" t="n">
+        <v>244008</v>
+      </c>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5665,6 +5996,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 23명</t>
         </is>
       </c>
+      <c r="N91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -5680,7 +6012,9 @@
           <t>성결대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr"/>
+      <c r="D92" s="3" t="n">
+        <v>241025</v>
+      </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5722,6 +6056,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
         </is>
       </c>
+      <c r="N92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -5737,7 +6072,9 @@
           <t>성공회대학교 도서관</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr"/>
+      <c r="D93" s="3" t="n">
+        <v>211039</v>
+      </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5779,6 +6116,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -5794,7 +6132,9 @@
           <t>성균관대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr"/>
+      <c r="D94" s="3" t="n">
+        <v>211040</v>
+      </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5836,6 +6176,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 51명</t>
         </is>
       </c>
+      <c r="N94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -5851,7 +6192,9 @@
           <t>성신여자대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr"/>
+      <c r="D95" s="3" t="n">
+        <v>211041</v>
+      </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5893,6 +6236,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 46명</t>
         </is>
       </c>
+      <c r="N95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -5908,7 +6252,9 @@
           <t>세명대학교 민송도서관</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr"/>
+      <c r="D96" s="3" t="n">
+        <v>243004</v>
+      </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5950,6 +6296,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 4명</t>
         </is>
       </c>
+      <c r="N96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -5965,7 +6312,9 @@
           <t>세종대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr"/>
+      <c r="D97" s="3" t="n">
+        <v>211042</v>
+      </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -6007,6 +6356,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 10명</t>
         </is>
       </c>
+      <c r="N97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -6022,7 +6372,9 @@
           <t>세한대학교 도서관</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr"/>
+      <c r="D98" s="3" t="n">
+        <v>246014</v>
+      </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -6064,6 +6416,7 @@
           <t>[교육부고시 비고] 구)대불대학교('12 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 25명</t>
         </is>
       </c>
+      <c r="N98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -6079,7 +6432,9 @@
           <t>송원대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr"/>
+      <c r="D99" s="3" t="n">
+        <v>224009</v>
+      </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -6121,6 +6476,7 @@
           <t>[교육부고시 비고] 전문→일반('12) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 6명</t>
         </is>
       </c>
+      <c r="N99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -6136,7 +6492,9 @@
           <t>수원가톨릭대학교 도서관</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr"/>
+      <c r="D100" s="3" t="n">
+        <v>241030</v>
+      </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -6178,6 +6536,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -6193,7 +6552,9 @@
           <t>수원대학교 도서관</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr"/>
+      <c r="D101" s="3" t="n">
+        <v>241031</v>
+      </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -6235,6 +6596,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 6명</t>
         </is>
       </c>
+      <c r="N101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -6250,7 +6612,9 @@
           <t>숙명여자대학교 도서관</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr"/>
+      <c r="D102" s="3" t="n">
+        <v>211043</v>
+      </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -6292,6 +6656,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 63명</t>
         </is>
       </c>
+      <c r="N102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -6307,7 +6672,9 @@
           <t>국립순천대학교 도서관</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr"/>
+      <c r="D103" s="3" t="n">
+        <v>246008</v>
+      </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6349,6 +6716,7 @@
           <t>[교육부고시 비고] 구)순천대학교('24 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 18명</t>
         </is>
       </c>
+      <c r="N103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -6364,7 +6732,9 @@
           <t>순천향대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr"/>
+      <c r="D104" s="3" t="n">
+        <v>244009</v>
+      </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -6406,6 +6776,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 5명</t>
         </is>
       </c>
+      <c r="N104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -6421,7 +6792,9 @@
           <t>숭실대학교 도서관</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr"/>
+      <c r="D105" s="3" t="n">
+        <v>211044</v>
+      </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6463,6 +6836,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 117명</t>
         </is>
       </c>
+      <c r="N105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -6478,7 +6852,9 @@
           <t>화성의과학대학교 도서관</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr"/>
+      <c r="D106" s="3" t="n">
+        <v>241103</v>
+      </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6520,6 +6896,7 @@
           <t>[교육부고시 비고] 구)신경대학교('22.9.1 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 0명</t>
         </is>
       </c>
+      <c r="N106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -6535,7 +6912,9 @@
           <t>신라대학교 도서관</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr"/>
+      <c r="D107" s="3" t="n">
+        <v>221020</v>
+      </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6577,6 +6956,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 33명</t>
         </is>
       </c>
+      <c r="N107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -6592,7 +6972,9 @@
           <t>신한대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr"/>
+      <c r="D108" s="3" t="n">
+        <v>241096</v>
+      </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6634,6 +7016,7 @@
           <t>[교육부고시 비고] 한북대학교+신흥대학교(일반+전문)('14) / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 5명</t>
         </is>
       </c>
+      <c r="N108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -6649,7 +7032,9 @@
           <t>아신대학교 도서관</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr"/>
+      <c r="D109" s="3" t="n">
+        <v>241037</v>
+      </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6691,6 +7076,7 @@
           <t>[교육부고시 비고] 구)아세아연합신학대학교('21 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
         </is>
       </c>
+      <c r="N109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -6706,7 +7092,9 @@
           <t>아주대학교 도서관; 아주대학교 의학문헌정보센터</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr"/>
+      <c r="D110" s="3" t="n">
+        <v>241038</v>
+      </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6746,6 +7134,11 @@
       <c r="M110" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 아주대학교 도서관; 아주대학교 의학문헌정보센터 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 38명</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
+          <t>아주대학교의학문헌정보센터: 241074</t>
         </is>
       </c>
     </row>
@@ -6763,7 +7156,9 @@
           <t>국립경국대학교 예천캠퍼스도서관; 국립경국대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr"/>
+      <c r="D111" s="3" t="n">
+        <v>247015</v>
+      </c>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6805,6 +7200,7 @@
           <t>[교육부고시 비고] 구)국립안동대학교('25,3.1 변경) / 대학도서관 통계 2개 캠퍼스 통합: 국립경국대학교 예천캠퍼스도서관; 국립경국대학교 중앙도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 11명</t>
         </is>
       </c>
+      <c r="N111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -6820,7 +7216,9 @@
           <t>안양대학교 도서관</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr"/>
+      <c r="D112" s="3" t="n">
+        <v>241012</v>
+      </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6862,6 +7260,7 @@
           <t>장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 3명</t>
         </is>
       </c>
+      <c r="N112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -6877,7 +7276,9 @@
           <t>연세대학교 의학도서관; 연세대학교 학술문화처 도서관</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr"/>
+      <c r="D113" s="3" t="n">
+        <v>211046</v>
+      </c>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6917,6 +7318,11 @@
       <c r="M113" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 연세대학교 의학도서관; 연세대학교 학술문화처 도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 69명</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
+          <t>연세대학교 의학도서관: 211072</t>
         </is>
       </c>
     </row>
@@ -6934,7 +7340,9 @@
           <t>연세대학교(미래) 원주캠퍼스 의학도서관; 연세대학교(미래) 학술정보원</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr"/>
+      <c r="D114" s="3" t="n">
+        <v>242009</v>
+      </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6974,6 +7382,11 @@
       <c r="M114" s="3" t="inlineStr">
         <is>
           <t>교육부 고시상 본교와 별도의 독립 학교(분교)로 등재 - 도서관 통계도 별도 / 대학도서관 통계 2개 캠퍼스 통합: 연세대학교(미래) 원주캠퍼스 의학도서관; 연세대학교(미래) 학술정보원 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 14명</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
+          <t>연세대학교(미래) 원주캠퍼스 의학도서관: 242018</t>
         </is>
       </c>
     </row>
@@ -6991,7 +7404,9 @@
           <t>영남대학교 도서관; 영남대학교 의과대학 의학도서관</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr"/>
+      <c r="D115" s="3" t="n">
+        <v>247017</v>
+      </c>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -7031,6 +7446,11 @@
       <c r="M115" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 영남대학교 도서관; 영남대학교 의과대학 의학도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 6명</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
+          <t>영남대학교 의과대학 의학도서관: 322007</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7468,9 @@
           <t>영남신학대학교 도서관</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr"/>
+      <c r="D116" s="3" t="n">
+        <v>247018</v>
+      </c>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -7090,6 +7512,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 4명</t>
         </is>
       </c>
+      <c r="N116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -7105,7 +7528,9 @@
           <t>영산대학교 도서관</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr"/>
+      <c r="D117" s="3" t="n">
+        <v>221024</v>
+      </c>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -7147,6 +7572,7 @@
           <t>[교육부고시 비고] 산업→일반('06) / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 29명</t>
         </is>
       </c>
+      <c r="N117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -7162,7 +7588,9 @@
           <t>영산선학대학교 도서관</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr"/>
+      <c r="D118" s="3" t="n">
+        <v>246010</v>
+      </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -7204,6 +7632,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 0명</t>
         </is>
       </c>
+      <c r="N118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -7219,7 +7648,9 @@
           <t>예수대학교 도서관</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr"/>
+      <c r="D119" s="3" t="n">
+        <v>245007</v>
+      </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -7261,6 +7692,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 0명</t>
         </is>
       </c>
+      <c r="N119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -7276,7 +7708,9 @@
           <t>예원예술대학교 도서관</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr"/>
+      <c r="D120" s="3" t="n">
+        <v>245027</v>
+      </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -7318,6 +7752,7 @@
           <t>장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 12명</t>
         </is>
       </c>
+      <c r="N120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -7333,7 +7768,9 @@
           <t>용인대학교 도서관</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr"/>
+      <c r="D121" s="3" t="n">
+        <v>241015</v>
+      </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -7375,6 +7812,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 5명</t>
         </is>
       </c>
+      <c r="N121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -7390,7 +7828,9 @@
           <t>우석대학교 도서관</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr"/>
+      <c r="D122" s="3" t="n">
+        <v>245017</v>
+      </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -7432,6 +7872,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 40명</t>
         </is>
       </c>
+      <c r="N122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -7447,7 +7888,9 @@
           <t>우송대학교 우송도서관</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr"/>
+      <c r="D123" s="3" t="n">
+        <v>225019</v>
+      </c>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -7489,6 +7932,7 @@
           <t>[교육부고시 비고] 우송대학교+우송공업대학(산업+전문)('09) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 8명</t>
         </is>
       </c>
+      <c r="N123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -7504,7 +7948,9 @@
           <t>울산과학기술원 학술정보관</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr"/>
+      <c r="D124" s="3" t="n">
+        <v>231001</v>
+      </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7546,6 +7992,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -7561,7 +8008,9 @@
           <t>울산대학교 도서관</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr"/>
+      <c r="D125" s="3" t="n">
+        <v>248009</v>
+      </c>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7603,6 +8052,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 8명</t>
         </is>
       </c>
+      <c r="N125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -7618,7 +8068,9 @@
           <t>원광대학교 도서관; 원광보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr"/>
+      <c r="D126" s="3" t="n">
+        <v>245008</v>
+      </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7658,6 +8110,11 @@
       <c r="M126" s="3" t="inlineStr">
         <is>
           <t>통폐합: 구 '원광보건대학교' → 2026.2. 원광대학교로 흡수통합 / [교육부고시 비고] 원광대학교+원광보건대학교(일반+전문)('26) / 대학도서관 통계 2개 캠퍼스 통합: 원광대학교 도서관; 원광보건대학교 도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 22명</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
+          <t>원광보건대학교 도서관: 245009</t>
         </is>
       </c>
     </row>
@@ -7675,7 +8132,9 @@
           <t>위덕대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr"/>
+      <c r="D127" s="3" t="n">
+        <v>247032</v>
+      </c>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7717,6 +8176,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 17명</t>
         </is>
       </c>
+      <c r="N127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -7732,7 +8192,9 @@
           <t>유원대학교 도서관</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr"/>
+      <c r="D128" s="3" t="n">
+        <v>243013</v>
+      </c>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7774,6 +8236,7 @@
           <t>[교육부고시 비고] 구)영동대학교('16.9. 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 14명</t>
         </is>
       </c>
+      <c r="N128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -7789,7 +8252,9 @@
           <t>을지대학교 대전캠퍼스 학술정보원</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr"/>
+      <c r="D129" s="3" t="n">
+        <v>230001</v>
+      </c>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7831,6 +8296,7 @@
           <t>[교육부고시 비고] 을지대학교+서울보건대학(일반+전문)('07) / 장애학생지원센터 통계: 있음(O) (캠퍼스 3개 통합집계) · 장애재학생수(학부) 합계 6명</t>
         </is>
       </c>
+      <c r="N129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -7846,7 +8312,9 @@
           <t>이화여자대학교 도서관</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr"/>
+      <c r="D130" s="3" t="n">
+        <v>211048</v>
+      </c>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7888,6 +8356,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 62명</t>
         </is>
       </c>
+      <c r="N130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -7903,7 +8372,9 @@
           <t>인제대학교 백인제기념도서관; 인제대학교 의학도서관</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr"/>
+      <c r="D131" s="3" t="n">
+        <v>248012</v>
+      </c>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7943,6 +8414,11 @@
       <c r="M131" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 인제대학교 백인제기념도서관; 인제대학교 의학도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 19명</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
+          <t>인제대학교의학도서관: 221025</t>
         </is>
       </c>
     </row>
@@ -7960,7 +8436,9 @@
           <t>인천가톨릭대학교 도서관; 인천가톨릭대학교 송도국제캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr"/>
+      <c r="D132" s="3" t="n">
+        <v>223011</v>
+      </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -8000,6 +8478,11 @@
       <c r="M132" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 인천가톨릭대학교 도서관; 인천가톨릭대학교 송도국제캠퍼스 도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 6명</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
+          <t>인천가톨릭대학교 송도국제캠퍼스 도서관: 228002</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8500,9 @@
           <t>인천대학교 도서관</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr"/>
+      <c r="D133" s="3" t="n">
+        <v>223006</v>
+      </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -8059,6 +8544,7 @@
           <t>[교육부고시 비고] 인천대학교+인천전문대학(일반+전문)('10), 설립변경(공립→국립대법인)('13) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 116명</t>
         </is>
       </c>
+      <c r="N133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -8074,7 +8560,9 @@
           <t>인하대학교 정석학술정보관</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr"/>
+      <c r="D134" s="3" t="n">
+        <v>223009</v>
+      </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -8116,6 +8604,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -8131,7 +8620,9 @@
           <t>장로회신학대학교 도서관</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr"/>
+      <c r="D135" s="3" t="n">
+        <v>211050</v>
+      </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -8173,6 +8664,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 5명</t>
         </is>
       </c>
+      <c r="N135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -8188,7 +8680,9 @@
           <t>전남대학교 도서관</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr"/>
+      <c r="D136" s="3" t="n">
+        <v>224010</v>
+      </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -8230,6 +8724,7 @@
           <t>[교육부고시 비고] 전남대학교+여수대학교(일반+산업)('06) / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 89명</t>
         </is>
       </c>
+      <c r="N136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -8245,7 +8740,9 @@
           <t>전북대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr"/>
+      <c r="D137" s="3" t="n">
+        <v>245011</v>
+      </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -8287,6 +8784,7 @@
           <t>[교육부고시 비고] 전북대학교+익산대학(일반+전문)('08) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 27명</t>
         </is>
       </c>
+      <c r="N137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -8302,7 +8800,9 @@
           <t>전주대학교 도서관</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr"/>
+      <c r="D138" s="3" t="n">
+        <v>245016</v>
+      </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -8344,6 +8844,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 24명</t>
         </is>
       </c>
+      <c r="N138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -8408,7 +8909,9 @@
           <t>제주대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr"/>
+      <c r="D140" s="3" t="n">
+        <v>249002</v>
+      </c>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -8450,6 +8953,7 @@
           <t>[교육부고시 비고] 제주대학교+제주교육대학교(일반+교육)('08) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 53명</t>
         </is>
       </c>
+      <c r="N140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -8465,7 +8969,9 @@
           <t>조선대학교 도서관</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr"/>
+      <c r="D141" s="3" t="n">
+        <v>224011</v>
+      </c>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -8507,6 +9013,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 49명</t>
         </is>
       </c>
+      <c r="N141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -8522,7 +9029,9 @@
           <t>중부대학교 도서관</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr"/>
+      <c r="D142" s="3" t="n">
+        <v>244011</v>
+      </c>
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -8564,6 +9073,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 14명</t>
         </is>
       </c>
+      <c r="N142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -8579,7 +9089,9 @@
           <t>중앙대학교 서울캠퍼스 학술정보원; 중앙대학교 제2캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr"/>
+      <c r="D143" s="3" t="n">
+        <v>211052</v>
+      </c>
       <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8619,6 +9131,11 @@
       <c r="M143" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 중앙대학교+적십자간호대학(일반+전문)('12), 분교(안성)→제2캠퍼스('12) / 대학도서관 통계 2개 캠퍼스 통합: 중앙대학교 서울캠퍼스 학술정보원; 중앙대학교 제2캠퍼스 도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 32명</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
+          <t>중앙대학교 제2캠퍼스 도서관: 241044</t>
         </is>
       </c>
     </row>
@@ -8636,7 +9153,9 @@
           <t>중앙승가대학교 도서관</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr"/>
+      <c r="D144" s="3" t="n">
+        <v>211053</v>
+      </c>
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8678,6 +9197,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -8693,7 +9213,9 @@
           <t>중원대학교 도서관</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr"/>
+      <c r="D145" s="3" t="n">
+        <v>243023</v>
+      </c>
       <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8735,6 +9257,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 10명</t>
         </is>
       </c>
+      <c r="N145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -8807,7 +9330,9 @@
           <t>창신대학교 도서관</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr"/>
+      <c r="D147" s="3" t="n">
+        <v>248017</v>
+      </c>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8849,6 +9374,7 @@
           <t>[교육부고시 비고] 전문→일반('13) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 11명</t>
         </is>
       </c>
+      <c r="N147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -8864,7 +9390,9 @@
           <t>경남도립거창대학 도서관; 경남도립남해대학 도서관; 국립창원대학교 도서관</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr"/>
+      <c r="D148" s="3" t="n">
+        <v>248019</v>
+      </c>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8904,6 +9432,11 @@
       <c r="M148" s="3" t="inlineStr">
         <is>
           <t>통폐합: 구 '경남도립거창대학' → 2026.3. 국립창원대학교로 통합 / 통폐합: 구 '경남도립남해대학' → 2026.3. 국립창원대학교로 통합 / [교육부고시 비고] 구) 창원대학교('24 변경), 국립창원대학교+경남도립거창대학+경남도립남해대학(일반+전문+전문)('26) / 대학도서관 통계 3개 캠퍼스 통합: 경남도립거창대학 도서관; 경남도립남해대학 도서관; 국립창원대학교 도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 3개 통합집계) · 장애재학생수(학부) 합계 61명</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
+          <t>국립창원대학교 거창캠퍼스도서관: 248024; 국립창원대학교 남해캠퍼스도서관(남해책마루도서관): 248025</t>
         </is>
       </c>
     </row>
@@ -8921,7 +9454,9 @@
           <t>청주대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr"/>
+      <c r="D149" s="3" t="n">
+        <v>243007</v>
+      </c>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8963,6 +9498,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 3명</t>
         </is>
       </c>
+      <c r="N149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -8978,7 +9514,9 @@
           <t>초당대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr"/>
+      <c r="D150" s="3" t="n">
+        <v>246016</v>
+      </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -9020,6 +9558,7 @@
           <t>[교육부고시 비고] 산업→일반('12) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 10명</t>
         </is>
       </c>
+      <c r="N150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -9035,7 +9574,9 @@
           <t>총신대학교 도서관</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr"/>
+      <c r="D151" s="3" t="n">
+        <v>211054</v>
+      </c>
       <c r="E151" s="2" t="inlineStr"/>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -9077,6 +9618,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 47명</t>
         </is>
       </c>
+      <c r="N151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -9092,7 +9634,9 @@
           <t>추계예술대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr"/>
+      <c r="D152" s="3" t="n">
+        <v>211055</v>
+      </c>
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -9134,6 +9678,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 13명</t>
         </is>
       </c>
+      <c r="N152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -9149,7 +9694,9 @@
           <t>충남대학교 도서관</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr"/>
+      <c r="D153" s="3" t="n">
+        <v>225009</v>
+      </c>
       <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -9191,6 +9738,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 110명</t>
         </is>
       </c>
+      <c r="N153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -9206,7 +9754,9 @@
           <t>충북대학교 도서관</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr"/>
+      <c r="D154" s="3" t="n">
+        <v>243009</v>
+      </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -9248,6 +9798,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 122명</t>
         </is>
       </c>
+      <c r="N154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -9263,7 +9814,9 @@
           <t>칼빈대학교 도서관</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr"/>
+      <c r="D155" s="3" t="n">
+        <v>241063</v>
+      </c>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -9305,6 +9858,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 1명</t>
         </is>
       </c>
+      <c r="N155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -9320,7 +9874,9 @@
           <t>강서대학교 도서관</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr"/>
+      <c r="D156" s="3" t="n">
+        <v>211016</v>
+      </c>
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -9362,6 +9918,7 @@
           <t>[교육부고시 비고] 구)케이씨대학교('22.4.19) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 8명</t>
         </is>
       </c>
+      <c r="N156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -9377,7 +9934,9 @@
           <t>평택대학교 도서관</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr"/>
+      <c r="D157" s="3" t="n">
+        <v>241046</v>
+      </c>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -9419,6 +9978,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 9명</t>
         </is>
       </c>
+      <c r="N157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -9434,7 +9994,9 @@
           <t>포항공과대학교 박태준학술정보관</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr"/>
+      <c r="D158" s="3" t="n">
+        <v>247020</v>
+      </c>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -9476,6 +10038,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 0명</t>
         </is>
       </c>
+      <c r="N158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -9491,7 +10054,9 @@
           <t>한경국립대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr"/>
+      <c r="D159" s="3" t="n">
+        <v>241039</v>
+      </c>
       <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -9533,6 +10098,7 @@
           <t>[교육부고시 비고] 산업→일반('12), 한경대학교+한국복지대학교(일반+전문)('23 3.1 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 230명</t>
         </is>
       </c>
+      <c r="N159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -9548,7 +10114,9 @@
           <t>한국공학대학교 도서관</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr"/>
+      <c r="D160" s="3" t="n">
+        <v>241069</v>
+      </c>
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -9590,6 +10158,7 @@
           <t>[교육부고시 비고] 산업→일반(('12 변경), 구)한국산업기술대학교('22 3.1 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 5명</t>
         </is>
       </c>
+      <c r="N160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -9605,7 +10174,9 @@
           <t>한국과학기술원 학술문화관</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr"/>
+      <c r="D161" s="3" t="n">
+        <v>325007</v>
+      </c>
       <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -9647,6 +10218,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -9662,7 +10234,9 @@
           <t>한국교원대학교 도서관</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr"/>
+      <c r="D162" s="3" t="n">
+        <v>243012</v>
+      </c>
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -9704,6 +10278,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 48명</t>
         </is>
       </c>
+      <c r="N162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -9719,7 +10294,9 @@
           <t>국립한국교통대학교 도서관</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr"/>
+      <c r="D163" s="3" t="n">
+        <v>243010</v>
+      </c>
       <c r="E163" s="2" t="inlineStr"/>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9761,6 +10338,7 @@
           <t>[교육부고시 비고] 충주대학교+청주과학대학(산업+전문)('06), 산업→일반('10), 충주대학교+한국철도대학(일반+전문)('12), 구)한국교통대학교('24 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 36명</t>
         </is>
       </c>
+      <c r="N163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -9776,7 +10354,9 @@
           <t>한국기술교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr"/>
+      <c r="D164" s="3" t="n">
+        <v>244013</v>
+      </c>
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9818,6 +10398,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
         </is>
       </c>
+      <c r="N164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -9833,7 +10414,9 @@
           <t>한국성서대학교 도서관</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr"/>
+      <c r="D165" s="3" t="n">
+        <v>211058</v>
+      </c>
       <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9875,6 +10458,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 18명</t>
         </is>
       </c>
+      <c r="N165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -9890,7 +10474,9 @@
           <t>한국에너지공과대학교 도서관</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr"/>
+      <c r="D166" s="3" t="n">
+        <v>246029</v>
+      </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9932,6 +10518,7 @@
           <t>[교육부고시 비고] ('22년 3.2) / 장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -9947,7 +10534,9 @@
           <t>한국외국어대학교 글로벌캠퍼스 도서관; 한국외국어대학교 도서관</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr"/>
+      <c r="D167" s="3" t="n">
+        <v>211059</v>
+      </c>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9987,6 +10576,11 @@
       <c r="M167" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 본분교 통합('14) / 대학도서관 통계 2개 캠퍼스 통합: 한국외국어대학교 글로벌캠퍼스 도서관; 한국외국어대학교 도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 6명</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
+          <t>한국외국어대학교 글로벌캠퍼스 도서관: 241047</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10598,9 @@
           <t>한국전통문화대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr"/>
+      <c r="D168" s="3" t="n">
+        <v>244031</v>
+      </c>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -10046,6 +10642,7 @@
           <t>[교육부고시 비고] 구)한국전통문화학교('12 변경) / 장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -10061,7 +10658,9 @@
           <t>한국체육대학교 도서관</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr"/>
+      <c r="D169" s="3" t="n">
+        <v>211060</v>
+      </c>
       <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -10103,6 +10702,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 19명</t>
         </is>
       </c>
+      <c r="N169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -10118,7 +10718,9 @@
           <t>한국침례신학대학교 도서관</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr"/>
+      <c r="D170" s="3" t="n">
+        <v>225012</v>
+      </c>
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -10160,6 +10762,7 @@
           <t>[교육부고시 비고] 침례신학대학교+수도침례신학교(일반+각종학교)('06), 구)침례신학대학교('20 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 16명</t>
         </is>
       </c>
+      <c r="N170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -10175,7 +10778,9 @@
           <t>한국항공대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr"/>
+      <c r="D171" s="3" t="n">
+        <v>241048</v>
+      </c>
       <c r="E171" s="2" t="inlineStr"/>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -10217,6 +10822,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -10232,7 +10838,9 @@
           <t>국립한국해양대학교 도서관</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr"/>
+      <c r="D172" s="3" t="n">
+        <v>221028</v>
+      </c>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -10274,6 +10882,7 @@
           <t>[교육부고시 비고] 구)한국해양대학교('24 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 6명</t>
         </is>
       </c>
+      <c r="N172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -10289,7 +10898,9 @@
           <t>한남대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr"/>
+      <c r="D173" s="3" t="n">
+        <v>225013</v>
+      </c>
       <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -10331,6 +10942,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 11명</t>
         </is>
       </c>
+      <c r="N173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -10346,7 +10958,9 @@
           <t>한동대학교 국제법률대학원 도서관; 한동대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr"/>
+      <c r="D174" s="3" t="n">
+        <v>247041</v>
+      </c>
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -10386,6 +11000,11 @@
       <c r="M174" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 한동대학교 국제법률대학원 도서관; 한동대학교 학술정보관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 9명</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
+          <t>한동대학교 학술정보관: 247030</t>
         </is>
       </c>
     </row>
@@ -10403,7 +11022,9 @@
           <t>한라대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr"/>
+      <c r="D175" s="3" t="n">
+        <v>242017</v>
+      </c>
       <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -10445,6 +11066,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -10460,7 +11082,9 @@
           <t>한림대학교 일송기념도서관</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr"/>
+      <c r="D176" s="3" t="n">
+        <v>242014</v>
+      </c>
       <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -10502,6 +11126,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 5명</t>
         </is>
       </c>
+      <c r="N176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -10517,7 +11142,9 @@
           <t>국립한밭대학교 도서관</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr"/>
+      <c r="D177" s="3" t="n">
+        <v>225001</v>
+      </c>
       <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -10559,6 +11186,7 @@
           <t>[교육부고시 비고] 산업→일반('12), 구)한밭대학교('24 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 27명</t>
         </is>
       </c>
+      <c r="N177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -10574,7 +11202,9 @@
           <t>한서대학교 도서관</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr"/>
+      <c r="D178" s="3" t="n">
+        <v>244015</v>
+      </c>
       <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -10616,6 +11246,7 @@
           <t>장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -10631,7 +11262,9 @@
           <t>한성대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr"/>
+      <c r="D179" s="3" t="n">
+        <v>211061</v>
+      </c>
       <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -10673,6 +11306,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 4명</t>
         </is>
       </c>
+      <c r="N179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -10688,7 +11322,9 @@
           <t>한세대학교 도서관</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr"/>
+      <c r="D180" s="3" t="n">
+        <v>241034</v>
+      </c>
       <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -10730,6 +11366,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 23명</t>
         </is>
       </c>
+      <c r="N180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -10745,7 +11382,9 @@
           <t>한신대학교 신학대학원 장공도서관; 한신대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr"/>
+      <c r="D181" s="3" t="n">
+        <v>241049</v>
+      </c>
       <c r="E181" s="2" t="inlineStr"/>
       <c r="F181" s="2" t="inlineStr">
         <is>
@@ -10785,6 +11424,11 @@
       <c r="M181" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 한신대학교 신학대학원 장공도서관; 한신대학교 중앙도서관 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 1명</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
+          <t>한신대학교 신학대학원 장공도서관: 211069</t>
         </is>
       </c>
     </row>
@@ -10802,7 +11446,9 @@
           <t>한양대학교 백남학술정보관</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr"/>
+      <c r="D182" s="3" t="n">
+        <v>211062</v>
+      </c>
       <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr">
         <is>
@@ -10844,6 +11490,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 38명</t>
         </is>
       </c>
+      <c r="N182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -10859,7 +11506,9 @@
           <t>한양대학교(ERICA) ERICA학술정보관</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr"/>
+      <c r="D183" s="3" t="n">
+        <v>241050</v>
+      </c>
       <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -10901,6 +11550,7 @@
           <t>교육부 고시상 본교와 별도의 독립 학교(분교)로 등재 - 도서관 통계도 별도 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 25명</t>
         </is>
       </c>
+      <c r="N183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -10916,7 +11566,9 @@
           <t>한일장신대학교 도서관</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr"/>
+      <c r="D184" s="3" t="n">
+        <v>245018</v>
+      </c>
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -10958,6 +11610,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
         </is>
       </c>
+      <c r="N184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -10973,7 +11626,9 @@
           <t>협성대학교 도서관</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr"/>
+      <c r="D185" s="3" t="n">
+        <v>241052</v>
+      </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -11015,6 +11670,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 91명</t>
         </is>
       </c>
+      <c r="N185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -11030,7 +11686,9 @@
           <t>호남대학교 도서관</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr"/>
+      <c r="D186" s="3" t="n">
+        <v>224014</v>
+      </c>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -11072,6 +11730,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 24명</t>
         </is>
       </c>
+      <c r="N186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -11087,7 +11746,9 @@
           <t>호남신학대학교 도서관</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr"/>
+      <c r="D187" s="3" t="n">
+        <v>224015</v>
+      </c>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -11129,6 +11790,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
         </is>
       </c>
+      <c r="N187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -11144,7 +11806,9 @@
           <t>호서대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr"/>
+      <c r="D188" s="3" t="n">
+        <v>244019</v>
+      </c>
       <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -11186,6 +11850,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 7명</t>
         </is>
       </c>
+      <c r="N188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -11201,7 +11866,9 @@
           <t>홍익대학교 문정 도서관; 홍익대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr"/>
+      <c r="D189" s="3" t="n">
+        <v>211064</v>
+      </c>
       <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -11241,6 +11908,11 @@
       <c r="M189" s="3" t="inlineStr">
         <is>
           <t>대학도서관 통계 2개 캠퍼스 통합: 홍익대학교 문정 도서관; 홍익대학교 중앙도서관 / 장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 13명</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
+          <t>홍익대학교 문정도서관: 244026</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11930,9 @@
           <t>경인교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr"/>
+      <c r="D190" s="3" t="n">
+        <v>223005</v>
+      </c>
       <c r="E190" s="2" t="inlineStr"/>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -11300,6 +11974,7 @@
           <t>장애학생지원센터 통계: 있음(O) (캠퍼스 2개 통합집계) · 장애재학생수(학부) 합계 68명</t>
         </is>
       </c>
+      <c r="N190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -11315,7 +11990,9 @@
           <t>공주교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr"/>
+      <c r="D191" s="3" t="n">
+        <v>244003</v>
+      </c>
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -11357,6 +12034,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 16명</t>
         </is>
       </c>
+      <c r="N191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -11372,7 +12050,9 @@
           <t>광주교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr"/>
+      <c r="D192" s="3" t="n">
+        <v>224002</v>
+      </c>
       <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -11414,6 +12094,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 19명</t>
         </is>
       </c>
+      <c r="N192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -11429,7 +12110,9 @@
           <t>대구교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr"/>
+      <c r="D193" s="3" t="n">
+        <v>222009</v>
+      </c>
       <c r="E193" s="2" t="inlineStr"/>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -11471,6 +12154,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 35명</t>
         </is>
       </c>
+      <c r="N193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -11486,7 +12170,9 @@
           <t>부산교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr"/>
+      <c r="D194" s="3" t="n">
+        <v>221015</v>
+      </c>
       <c r="E194" s="2" t="inlineStr"/>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -11528,6 +12214,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 44명</t>
         </is>
       </c>
+      <c r="N194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -11543,7 +12230,9 @@
           <t>서울교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr"/>
+      <c r="D195" s="3" t="n">
+        <v>211031</v>
+      </c>
       <c r="E195" s="2" t="inlineStr"/>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -11585,6 +12274,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 34명</t>
         </is>
       </c>
+      <c r="N195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -11600,7 +12290,9 @@
           <t>전주교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr"/>
+      <c r="D196" s="3" t="n">
+        <v>245015</v>
+      </c>
       <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -11642,6 +12334,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 9명</t>
         </is>
       </c>
+      <c r="N196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -11657,7 +12350,9 @@
           <t>진주교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr"/>
+      <c r="D197" s="3" t="n">
+        <v>248014</v>
+      </c>
       <c r="E197" s="2" t="inlineStr"/>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -11699,6 +12394,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 2명</t>
         </is>
       </c>
+      <c r="N197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -11714,7 +12410,9 @@
           <t>청주교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr"/>
+      <c r="D198" s="3" t="n">
+        <v>243006</v>
+      </c>
       <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -11756,6 +12454,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 21명</t>
         </is>
       </c>
+      <c r="N198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -11771,7 +12470,9 @@
           <t>춘천교육대학교 도서관</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr"/>
+      <c r="D199" s="3" t="n">
+        <v>242012</v>
+      </c>
       <c r="E199" s="2" t="inlineStr"/>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -11813,6 +12514,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 4명</t>
         </is>
       </c>
+      <c r="N199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -11828,7 +12530,9 @@
           <t>청운대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr"/>
+      <c r="D200" s="3" t="n">
+        <v>244028</v>
+      </c>
       <c r="E200" s="2" t="inlineStr"/>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -11870,6 +12574,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 3명</t>
         </is>
       </c>
+      <c r="N200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -11885,7 +12590,9 @@
           <t>호원대학교 도서관</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr"/>
+      <c r="D201" s="3" t="n">
+        <v>245013</v>
+      </c>
       <c r="E201" s="2" t="inlineStr"/>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -11927,6 +12634,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 0명</t>
         </is>
       </c>
+      <c r="N201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -11991,7 +12699,9 @@
           <t>순복음총회신학교 도서관</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr"/>
+      <c r="D203" s="3" t="n">
+        <v>243025</v>
+      </c>
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -12033,6 +12743,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 0명</t>
         </is>
       </c>
+      <c r="N203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -12048,7 +12759,9 @@
           <t>한국예술종합학교 예술정보관</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr"/>
+      <c r="D204" s="3" t="n">
+        <v>211068</v>
+      </c>
       <c r="E204" s="2" t="inlineStr"/>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -12090,6 +12803,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 12명</t>
         </is>
       </c>
+      <c r="N204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -12105,7 +12819,9 @@
           <t>한국방송통신대학교 도서관</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr"/>
+      <c r="D205" s="3" t="n">
+        <v>211057</v>
+      </c>
       <c r="E205" s="2" t="inlineStr"/>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -12147,6 +12863,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 528명</t>
         </is>
       </c>
+      <c r="N205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -12260,7 +12977,9 @@
           <t>고려사이버대학교 도서관</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr"/>
+      <c r="D208" s="3" t="n">
+        <v>211103</v>
+      </c>
       <c r="E208" s="2" t="inlineStr"/>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -12302,6 +13021,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 134명</t>
         </is>
       </c>
+      <c r="N208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -12317,7 +13037,9 @@
           <t>국제사이버대학교 도서관</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr"/>
+      <c r="D209" s="3" t="n">
+        <v>241080</v>
+      </c>
       <c r="E209" s="2" t="inlineStr"/>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -12359,6 +13081,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 82명</t>
         </is>
       </c>
+      <c r="N209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -12374,7 +13097,9 @@
           <t>글로벌사이버대학교 도서관</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr"/>
+      <c r="D210" s="3" t="n">
+        <v>244040</v>
+      </c>
       <c r="E210" s="2" t="inlineStr"/>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -12416,6 +13141,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 41명</t>
         </is>
       </c>
+      <c r="N210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -12431,7 +13157,9 @@
           <t>대구사이버대학교 전자도서관</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr"/>
+      <c r="D211" s="3" t="n">
+        <v>222020</v>
+      </c>
       <c r="E211" s="2" t="inlineStr"/>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -12473,6 +13201,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 93명</t>
         </is>
       </c>
+      <c r="N211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -12488,7 +13217,9 @@
           <t>디지털서울문화예술대학교 도서관</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr"/>
+      <c r="D212" s="3" t="n">
+        <v>211110</v>
+      </c>
       <c r="E212" s="2" t="inlineStr"/>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -12530,6 +13261,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 13명</t>
         </is>
       </c>
+      <c r="N212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -12545,7 +13277,9 @@
           <t>부산디지털대학교 도서관</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr"/>
+      <c r="D213" s="3" t="n">
+        <v>226006</v>
+      </c>
       <c r="E213" s="2" t="inlineStr"/>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -12587,6 +13321,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 108명</t>
         </is>
       </c>
+      <c r="N213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -12651,7 +13386,9 @@
           <t>서울디지털대학교 디지털도서관</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr"/>
+      <c r="D215" s="3" t="n">
+        <v>211104</v>
+      </c>
       <c r="E215" s="2" t="inlineStr"/>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -12693,6 +13430,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 241명</t>
         </is>
       </c>
+      <c r="N215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -12708,7 +13446,9 @@
           <t>서울사이버대학교 전자도서관</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr"/>
+      <c r="D216" s="3" t="n">
+        <v>211100</v>
+      </c>
       <c r="E216" s="2" t="inlineStr"/>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -12750,6 +13490,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 296명</t>
         </is>
       </c>
+      <c r="N216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -12761,7 +13502,9 @@
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr"/>
-      <c r="D217" s="2" t="inlineStr"/>
+      <c r="D217" s="3" t="n">
+        <v>211107</v>
+      </c>
       <c r="E217" s="2" t="inlineStr"/>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -12799,6 +13542,7 @@
           <t>KERIS 대학도서관 통계 없음 / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 334명</t>
         </is>
       </c>
+      <c r="N217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -12920,7 +13664,9 @@
           <t>한국열린사이버대학교 자료실</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr"/>
+      <c r="D220" s="3" t="n">
+        <v>211106</v>
+      </c>
       <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="inlineStr">
         <is>
@@ -12962,6 +13708,7 @@
           <t>[교육부고시 비고] 구)열린사이버대학교('16.7 변경) / 장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 559명</t>
         </is>
       </c>
+      <c r="N220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -13026,7 +13773,9 @@
           <t>화신사이버대학교 자료실</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr"/>
+      <c r="D222" s="3" t="n">
+        <v>226004</v>
+      </c>
       <c r="E222" s="2" t="inlineStr"/>
       <c r="F222" s="2" t="inlineStr">
         <is>
@@ -13068,6 +13817,7 @@
           <t>장애학생지원센터 통계: 있음(O) · 장애재학생수(학부) 합계 62명</t>
         </is>
       </c>
+      <c r="N222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -13083,7 +13833,9 @@
           <t>ICT폴리텍대학 도서관</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr"/>
+      <c r="D223" s="3" t="n">
+        <v>241100</v>
+      </c>
       <c r="E223" s="2" t="inlineStr"/>
       <c r="F223" s="2" t="inlineStr">
         <is>
@@ -13125,6 +13877,7 @@
           <t>[교육부고시 비고] 구)한국정보통신기능대학('15 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -13140,7 +13893,9 @@
           <t>한국폴리텍Ⅰ대학서울강서캠퍼스 도서관; 한국폴리텍Ⅰ대학서울정수캠퍼스 도서관; 한국폴리텍Ⅰ대학성남캠퍼스 도서관; 한국폴리텍Ⅰ대학제주캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr"/>
+      <c r="D224" s="3" t="n">
+        <v>211124</v>
+      </c>
       <c r="E224" s="2" t="inlineStr"/>
       <c r="F224" s="2" t="inlineStr">
         <is>
@@ -13180,6 +13935,11 @@
       <c r="M224" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 서울강서, 서울정수, 성남, 제주 / 대학도서관 통계 4개 캠퍼스 통합: 한국폴리텍Ⅰ대학서울강서캠퍼스 도서관; 한국폴리텍Ⅰ대학서울정수캠퍼스 도서관; 한국폴리텍Ⅰ대학성남캠퍼스 도서관; 한국폴리텍Ⅰ대학제주캠퍼스 도서관 / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
+          <t>한국폴리텍Ⅰ대학서울정수캠퍼스 도서관: 211123; 한국폴리텍Ⅰ대학성남캠퍼스 도서관: 241092; 한국폴리텍Ⅰ대학제주캠퍼스 도서관: 249008</t>
         </is>
       </c>
     </row>
@@ -13197,7 +13957,9 @@
           <t>한국폴리텍Ⅱ대학남인천캠퍼스 도서관; 한국폴리텍Ⅱ대학화성캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr"/>
+      <c r="D225" s="3" t="n">
+        <v>228005</v>
+      </c>
       <c r="E225" s="2" t="inlineStr"/>
       <c r="F225" s="2" t="inlineStr">
         <is>
@@ -13237,6 +13999,11 @@
       <c r="M225" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 인천, 남인천, 화성 / 대학도서관 통계 2개 캠퍼스 통합: 한국폴리텍Ⅱ대학남인천캠퍼스 도서관; 한국폴리텍Ⅱ대학화성캠퍼스 도서관 / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
+          <t>한국폴리텍Ⅱ대학화성캠퍼스 도서관: 241097</t>
         </is>
       </c>
     </row>
@@ -13254,7 +14021,9 @@
           <t>한국폴리텍Ⅲ대학강릉캠퍼스 도서관; 한국폴리텍Ⅲ대학원주캠퍼스 도서관; 한국폴리텍Ⅲ대학춘천캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr"/>
+      <c r="D226" s="3" t="n">
+        <v>242030</v>
+      </c>
       <c r="E226" s="2" t="inlineStr"/>
       <c r="F226" s="2" t="inlineStr">
         <is>
@@ -13294,6 +14063,11 @@
       <c r="M226" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 강릉, 원주, 춘천 / 대학도서관 통계 3개 캠퍼스 통합: 한국폴리텍Ⅲ대학강릉캠퍼스 도서관; 한국폴리텍Ⅲ대학원주캠퍼스 도서관; 한국폴리텍Ⅲ대학춘천캠퍼스 도서관 / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
+          <t>한국폴리텍Ⅲ대학원주캠퍼스 도서관: 242031; 한국폴리텍Ⅲ대학춘천캠퍼스 도서관: 242028</t>
         </is>
       </c>
     </row>
@@ -13311,7 +14085,9 @@
           <t>한국폴리텍Ⅳ대학아산캠퍼스 도서관; 한국폴리텍Ⅳ대학청주캠퍼스 도서관; 한국폴리텍Ⅳ대학충남캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr"/>
+      <c r="D227" s="3" t="n">
+        <v>144149</v>
+      </c>
       <c r="E227" s="2" t="inlineStr"/>
       <c r="F227" s="2" t="inlineStr">
         <is>
@@ -13351,6 +14127,11 @@
       <c r="M227" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 대전, 아산, 청주, 충남('24 변경) / 대학도서관 통계 3개 캠퍼스 통합: 한국폴리텍Ⅳ대학아산캠퍼스 도서관; 한국폴리텍Ⅳ대학청주캠퍼스 도서관; 한국폴리텍Ⅳ대학충남캠퍼스 도서관 / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
+          <t>한국폴리텍Ⅳ대학청주캠퍼스 도서관: 243026; 한국폴리텍Ⅳ대학충남캠퍼스 도서관: 230004</t>
         </is>
       </c>
     </row>
@@ -13368,7 +14149,9 @@
           <t>한국폴리텍Ⅴ대학광주캠퍼스 도서관; 한국폴리텍Ⅴ대학순천캠퍼스 도서관; 한국폴리텍Ⅴ대학익산캠퍼스 도서관; 한국폴리텍Ⅴ대학전남캠퍼스 도서관; 한국폴리텍Ⅴ대학전북캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr"/>
+      <c r="D228" s="3" t="n">
+        <v>246027</v>
+      </c>
       <c r="E228" s="2" t="inlineStr"/>
       <c r="F228" s="2" t="inlineStr">
         <is>
@@ -13408,6 +14191,11 @@
       <c r="M228" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 광주, 전북, 전남, 순천, 익산 / 대학도서관 통계 5개 캠퍼스 통합: 한국폴리텍Ⅴ대학광주캠퍼스 도서관; 한국폴리텍Ⅴ대학순천캠퍼스 도서관; 한국폴리텍Ⅴ대학익산캠퍼스 도서관; 한국폴리텍Ⅴ대학전남캠퍼스 도서관; 한국폴리텍Ⅴ대학전북캠퍼스 도서관 / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
+          <t>한국폴리텍Ⅴ대학광주캠퍼스 도서관: 코드 미확인; 한국폴리텍Ⅴ대학익산캠퍼스 도서관: 245031; 한국폴리텍Ⅴ대학전남캠퍼스 도서관: 246026; 한국폴리텍Ⅴ대학전북캠퍼스 도서관: 245029</t>
         </is>
       </c>
     </row>
@@ -13425,7 +14213,9 @@
           <t>한국폴리텍Ⅵ대학구미캠퍼스 도서관; 한국폴리텍Ⅵ대학대구캠퍼스 도서관; 한국폴리텍Ⅵ대학영남융합기술캠퍼스 도서관; 한국폴리텍Ⅵ대학영주캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr"/>
+      <c r="D229" s="3" t="n">
+        <v>247044</v>
+      </c>
       <c r="E229" s="2" t="inlineStr"/>
       <c r="F229" s="2" t="inlineStr">
         <is>
@@ -13465,6 +14255,11 @@
       <c r="M229" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 구미, 대구, 영주, 영남융합기술 / 대학도서관 통계 4개 캠퍼스 통합: 한국폴리텍Ⅵ대학구미캠퍼스 도서관; 한국폴리텍Ⅵ대학대구캠퍼스 도서관; 한국폴리텍Ⅵ대학영남융합기술캠퍼스 도서관; 한국폴리텍Ⅵ대학영주캠퍼스 도서관 / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
+          <t>한국폴리텍Ⅵ대학대구캠퍼스 도서관: 227005; 한국폴리텍Ⅵ대학영남융합기술캠퍼스 도서관: 227004; 한국폴리텍Ⅵ대학영주캠퍼스 도서관: 247046</t>
         </is>
       </c>
     </row>
@@ -13482,7 +14277,9 @@
           <t>한국폴리텍Ⅶ대학동부산캠퍼스 도서관; 한국폴리텍Ⅶ대학부산캠퍼스 도서관; 한국폴리텍Ⅶ대학울산캠퍼스 도서관; 한국폴리텍Ⅶ대학진주캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr"/>
+      <c r="D230" s="3" t="n">
+        <v>226005</v>
+      </c>
       <c r="E230" s="2" t="inlineStr"/>
       <c r="F230" s="2" t="inlineStr">
         <is>
@@ -13522,6 +14319,11 @@
       <c r="M230" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 부산, 울산, 창원, 진주, 동부산 / 대학도서관 통계 4개 캠퍼스 통합: 한국폴리텍Ⅶ대학동부산캠퍼스 도서관; 한국폴리텍Ⅶ대학부산캠퍼스 도서관; 한국폴리텍Ⅶ대학울산캠퍼스 도서관; 한국폴리텍Ⅶ대학진주캠퍼스 도서관 / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
+          <t>한국폴리텍Ⅶ대학부산캠퍼스 도서관: 226002; 한국폴리텍Ⅶ대학울산캠퍼스 도서관: 231003; 한국폴리텍Ⅶ대학진주캠퍼스 도서관: 코드 미확인</t>
         </is>
       </c>
     </row>
@@ -13539,7 +14341,9 @@
           <t>한국폴리텍특성화 로봇캠퍼스 도서관; 한국폴리텍특성화 바이오캠퍼스 도서관; 한국폴리텍특성화 반도체융합캠퍼스 도서관; 한국폴리텍특성화 항공캠퍼스 도서관</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr"/>
+      <c r="D231" s="3" t="n">
+        <v>247048</v>
+      </c>
       <c r="E231" s="2" t="inlineStr"/>
       <c r="F231" s="2" t="inlineStr">
         <is>
@@ -13579,6 +14383,11 @@
       <c r="M231" s="3" t="inlineStr">
         <is>
           <t>[교육부고시 비고] 바이오, 항공, 반도체융합, 로봇 / 대학도서관 통계 4개 캠퍼스 통합: 한국폴리텍특성화 로봇캠퍼스 도서관; 한국폴리텍특성화 바이오캠퍼스 도서관; 한국폴리텍특성화 반도체융합캠퍼스 도서관; 한국폴리텍특성화 항공캠퍼스 도서관 / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
+          <t>한국폴리텍특성화 바이오캠퍼스 도서관: 244041; 한국폴리텍특성화 반도체융합캠퍼스 도서관: 코드 미확인; 한국폴리텍특성화 항공캠퍼스 도서관: 248037</t>
         </is>
       </c>
     </row>
@@ -13596,7 +14405,9 @@
           <t>강동대학교 도서관</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr"/>
+      <c r="D232" s="3" t="n">
+        <v>243014</v>
+      </c>
       <c r="E232" s="2" t="inlineStr"/>
       <c r="F232" s="2" t="inlineStr">
         <is>
@@ -13638,6 +14449,7 @@
           <t>[교육부고시 비고] 구)극동정보대학('11 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -13653,7 +14465,9 @@
           <t>경기과학기술대학교 도서관</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr"/>
+      <c r="D233" s="3" t="n">
+        <v>241070</v>
+      </c>
       <c r="E233" s="2" t="inlineStr"/>
       <c r="F233" s="2" t="inlineStr">
         <is>
@@ -13695,6 +14509,7 @@
           <t>[교육부고시 비고] 구)경기공업대학('11 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -13710,7 +14525,9 @@
           <t>경북과학대학교 도서관</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr"/>
+      <c r="D234" s="3" t="n">
+        <v>247027</v>
+      </c>
       <c r="E234" s="2" t="inlineStr"/>
       <c r="F234" s="2" t="inlineStr">
         <is>
@@ -13752,6 +14569,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -13767,7 +14585,9 @@
           <t>경북보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr"/>
+      <c r="D235" s="3" t="n">
+        <v>247007</v>
+      </c>
       <c r="E235" s="2" t="inlineStr"/>
       <c r="F235" s="2" t="inlineStr">
         <is>
@@ -13809,6 +14629,7 @@
           <t>[교육부고시 비고] 구)김천과학대학교('15 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -13824,7 +14645,9 @@
           <t>계명문화대학교 도서관</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr"/>
+      <c r="D236" s="3" t="n">
+        <v>222005</v>
+      </c>
       <c r="E236" s="2" t="inlineStr"/>
       <c r="F236" s="2" t="inlineStr">
         <is>
@@ -13866,6 +14689,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -13881,7 +14705,9 @@
           <t>계원예술대학교 도서관</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr"/>
+      <c r="D237" s="3" t="n">
+        <v>241053</v>
+      </c>
       <c r="E237" s="2" t="inlineStr"/>
       <c r="F237" s="2" t="inlineStr">
         <is>
@@ -13923,6 +14749,7 @@
           <t>[교육부고시 비고] 구)계원디자인예술대학('12 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -13938,7 +14765,9 @@
           <t>구미대학교 도서관</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr"/>
+      <c r="D238" s="3" t="n">
+        <v>247033</v>
+      </c>
       <c r="E238" s="2" t="inlineStr"/>
       <c r="F238" s="2" t="inlineStr">
         <is>
@@ -13980,6 +14809,7 @@
           <t>[교육부고시 비고] 구)구미1대학('12 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -13995,7 +14825,9 @@
           <t>국제대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr"/>
+      <c r="D239" s="3" t="n">
+        <v>241064</v>
+      </c>
       <c r="E239" s="2" t="inlineStr"/>
       <c r="F239" s="2" t="inlineStr">
         <is>
@@ -14037,6 +14869,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -14052,7 +14885,9 @@
           <t>대경대학교 도서관</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr"/>
+      <c r="D240" s="3" t="n">
+        <v>247025</v>
+      </c>
       <c r="E240" s="2" t="inlineStr"/>
       <c r="F240" s="2" t="inlineStr">
         <is>
@@ -14094,6 +14929,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -14109,7 +14945,9 @@
           <t>대구공업대학교 도서관</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr"/>
+      <c r="D241" s="3" t="n">
+        <v>222008</v>
+      </c>
       <c r="E241" s="2" t="inlineStr"/>
       <c r="F241" s="2" t="inlineStr">
         <is>
@@ -14151,6 +14989,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -14166,7 +15005,9 @@
           <t>대구과학대학교 영송중앙도서관</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr"/>
+      <c r="D242" s="3" t="n">
+        <v>222011</v>
+      </c>
       <c r="E242" s="2" t="inlineStr"/>
       <c r="F242" s="2" t="inlineStr">
         <is>
@@ -14208,6 +15049,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -14223,7 +15065,9 @@
           <t>대덕대학교 도서관</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr"/>
+      <c r="D243" s="3" t="n">
+        <v>225011</v>
+      </c>
       <c r="E243" s="2" t="inlineStr"/>
       <c r="F243" s="2" t="inlineStr">
         <is>
@@ -14265,6 +15109,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -14280,7 +15125,9 @@
           <t>대동대학교 도서관</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr"/>
+      <c r="D244" s="3" t="n">
+        <v>221004</v>
+      </c>
       <c r="E244" s="2" t="inlineStr"/>
       <c r="F244" s="2" t="inlineStr">
         <is>
@@ -14322,6 +15169,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -14337,7 +15185,9 @@
           <t>대원대학교 도서관</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr"/>
+      <c r="D245" s="3" t="n">
+        <v>243015</v>
+      </c>
       <c r="E245" s="2" t="inlineStr"/>
       <c r="F245" s="2" t="inlineStr">
         <is>
@@ -14379,6 +15229,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -14394,7 +15245,9 @@
           <t>대전과학기술대학교 도서관</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr"/>
+      <c r="D246" s="3" t="n">
+        <v>225005</v>
+      </c>
       <c r="E246" s="2" t="inlineStr"/>
       <c r="F246" s="2" t="inlineStr">
         <is>
@@ -14436,6 +15289,7 @@
           <t>[교육부고시 비고] 구)혜천대학('14 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -14451,7 +15305,9 @@
           <t>대전보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr"/>
+      <c r="D247" s="3" t="n">
+        <v>225003</v>
+      </c>
       <c r="E247" s="2" t="inlineStr"/>
       <c r="F247" s="2" t="inlineStr">
         <is>
@@ -14493,6 +15349,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -14508,7 +15365,9 @@
           <t>동강대학교 도서관</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr"/>
+      <c r="D248" s="3" t="n">
+        <v>224007</v>
+      </c>
       <c r="E248" s="2" t="inlineStr"/>
       <c r="F248" s="2" t="inlineStr">
         <is>
@@ -14550,6 +15409,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -14565,7 +15425,9 @@
           <t>동서울대학교 학산도서관</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr"/>
+      <c r="D249" s="3" t="n">
+        <v>241013</v>
+      </c>
       <c r="E249" s="2" t="inlineStr"/>
       <c r="F249" s="2" t="inlineStr">
         <is>
@@ -14607,6 +15469,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -14622,7 +15485,9 @@
           <t>동원과학기술대학교 도서관</t>
         </is>
       </c>
-      <c r="D250" s="2" t="inlineStr"/>
+      <c r="D250" s="3" t="n">
+        <v>248039</v>
+      </c>
       <c r="E250" s="2" t="inlineStr"/>
       <c r="F250" s="2" t="inlineStr">
         <is>
@@ -14664,6 +15529,7 @@
           <t>[교육부고시 비고] 구)양산대학교('13 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -14679,7 +15545,9 @@
           <t>동의과학대학교 도서관</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr"/>
+      <c r="D251" s="3" t="n">
+        <v>221009</v>
+      </c>
       <c r="E251" s="2" t="inlineStr"/>
       <c r="F251" s="2" t="inlineStr">
         <is>
@@ -14721,6 +15589,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -14736,7 +15605,9 @@
           <t>두원공과대학교 도서관</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr"/>
+      <c r="D252" s="3" t="n">
+        <v>241054</v>
+      </c>
       <c r="E252" s="2" t="inlineStr"/>
       <c r="F252" s="2" t="inlineStr">
         <is>
@@ -14778,6 +15649,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -14793,7 +15665,9 @@
           <t>문경대학교 도서관</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr"/>
+      <c r="D253" s="3" t="n">
+        <v>247031</v>
+      </c>
       <c r="E253" s="2" t="inlineStr"/>
       <c r="F253" s="2" t="inlineStr">
         <is>
@@ -14835,6 +15709,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -14850,7 +15725,9 @@
           <t>백석문화대학교 도서관</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr"/>
+      <c r="D254" s="3" t="n">
+        <v>244023</v>
+      </c>
       <c r="E254" s="2" t="inlineStr"/>
       <c r="F254" s="2" t="inlineStr">
         <is>
@@ -14892,6 +15769,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -14907,7 +15785,9 @@
           <t>백제예술대학교 도서관</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr"/>
+      <c r="D255" s="3" t="n">
+        <v>245005</v>
+      </c>
       <c r="E255" s="2" t="inlineStr"/>
       <c r="F255" s="2" t="inlineStr">
         <is>
@@ -14949,6 +15829,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -14964,7 +15845,9 @@
           <t>부산경상대학교 도서관</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr"/>
+      <c r="D256" s="3" t="n">
+        <v>221013</v>
+      </c>
       <c r="E256" s="2" t="inlineStr"/>
       <c r="F256" s="2" t="inlineStr">
         <is>
@@ -15006,6 +15889,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -15021,7 +15905,9 @@
           <t>부산과학기술대학교 도서관</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr"/>
+      <c r="D257" s="3" t="n">
+        <v>221023</v>
+      </c>
       <c r="E257" s="2" t="inlineStr"/>
       <c r="F257" s="2" t="inlineStr">
         <is>
@@ -15063,6 +15949,7 @@
           <t>[교육부고시 비고] 구)부산정보대학('12 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -15078,7 +15965,9 @@
           <t>부산여자대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr"/>
+      <c r="D258" s="3" t="n">
+        <v>221021</v>
+      </c>
       <c r="E258" s="2" t="inlineStr"/>
       <c r="F258" s="2" t="inlineStr">
         <is>
@@ -15120,6 +16009,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -15135,7 +16025,9 @@
           <t>부산예술대학교 도서관</t>
         </is>
       </c>
-      <c r="D259" s="2" t="inlineStr"/>
+      <c r="D259" s="3" t="n">
+        <v>221029</v>
+      </c>
       <c r="E259" s="2" t="inlineStr"/>
       <c r="F259" s="2" t="inlineStr">
         <is>
@@ -15177,6 +16069,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -15192,7 +16085,9 @@
           <t>부천대학교 도서관</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr"/>
+      <c r="D260" s="3" t="n">
+        <v>241019</v>
+      </c>
       <c r="E260" s="2" t="inlineStr"/>
       <c r="F260" s="2" t="inlineStr">
         <is>
@@ -15234,6 +16129,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -15249,7 +16145,9 @@
           <t>서일대학교 도서관</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr"/>
+      <c r="D261" s="3" t="n">
+        <v>211038</v>
+      </c>
       <c r="E261" s="2" t="inlineStr"/>
       <c r="F261" s="2" t="inlineStr">
         <is>
@@ -15291,6 +16189,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -15306,7 +16205,9 @@
           <t>세경대학교 도서관</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr"/>
+      <c r="D262" s="3" t="n">
+        <v>242015</v>
+      </c>
       <c r="E262" s="2" t="inlineStr"/>
       <c r="F262" s="2" t="inlineStr">
         <is>
@@ -15348,6 +16249,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -15363,7 +16265,9 @@
           <t>송곡대학교 도서관</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr"/>
+      <c r="D263" s="3" t="n">
+        <v>242023</v>
+      </c>
       <c r="E263" s="2" t="inlineStr"/>
       <c r="F263" s="2" t="inlineStr">
         <is>
@@ -15405,6 +16309,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -15420,7 +16325,9 @@
           <t>송호대학교 도서관</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr"/>
+      <c r="D264" s="3" t="n">
+        <v>242022</v>
+      </c>
       <c r="E264" s="2" t="inlineStr"/>
       <c r="F264" s="2" t="inlineStr">
         <is>
@@ -15462,6 +16369,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -15477,7 +16385,9 @@
           <t>수원여자대학교 도서관</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr"/>
+      <c r="D265" s="3" t="n">
+        <v>241032</v>
+      </c>
       <c r="E265" s="2" t="inlineStr"/>
       <c r="F265" s="2" t="inlineStr">
         <is>
@@ -15519,6 +16429,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -15534,7 +16445,9 @@
           <t>순천제일대학교 도서관</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr"/>
+      <c r="D266" s="3" t="n">
+        <v>246007</v>
+      </c>
       <c r="E266" s="2" t="inlineStr"/>
       <c r="F266" s="2" t="inlineStr">
         <is>
@@ -15576,6 +16489,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -15591,7 +16505,9 @@
           <t>숭의여자대학교 학술정보센터</t>
         </is>
       </c>
-      <c r="D267" s="2" t="inlineStr"/>
+      <c r="D267" s="3" t="n">
+        <v>211045</v>
+      </c>
       <c r="E267" s="2" t="inlineStr"/>
       <c r="F267" s="2" t="inlineStr">
         <is>
@@ -15633,6 +16549,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -15648,7 +16565,9 @@
           <t>신구대학교 도서관</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr"/>
+      <c r="D268" s="3" t="n">
+        <v>241035</v>
+      </c>
       <c r="E268" s="2" t="inlineStr"/>
       <c r="F268" s="2" t="inlineStr">
         <is>
@@ -15690,6 +16609,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -15705,7 +16625,9 @@
           <t>신안산대학교 도서관</t>
         </is>
       </c>
-      <c r="D269" s="2" t="inlineStr"/>
+      <c r="D269" s="3" t="n">
+        <v>241101</v>
+      </c>
       <c r="E269" s="2" t="inlineStr"/>
       <c r="F269" s="2" t="inlineStr">
         <is>
@@ -15747,6 +16669,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -15762,7 +16685,9 @@
           <t>아주자동차대학교 도서관</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr"/>
+      <c r="D270" s="3" t="n">
+        <v>244038</v>
+      </c>
       <c r="E270" s="2" t="inlineStr"/>
       <c r="F270" s="2" t="inlineStr">
         <is>
@@ -15804,6 +16729,7 @@
           <t>[교육부고시 비고] 구)아주자동차대학('22.9.1 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -15819,7 +16745,9 @@
           <t>여주대학교 여암학술정보관</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr"/>
+      <c r="D271" s="3" t="n">
+        <v>241078</v>
+      </c>
       <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr">
         <is>
@@ -15861,6 +16789,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -15876,7 +16805,9 @@
           <t>연암대학교 도서관</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr"/>
+      <c r="D272" s="3" t="n">
+        <v>244010</v>
+      </c>
       <c r="E272" s="2" t="inlineStr"/>
       <c r="F272" s="2" t="inlineStr">
         <is>
@@ -15918,6 +16849,7 @@
           <t>[교육부고시 비고] 구)천안연암대학('16 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -15933,7 +16865,9 @@
           <t>영남외국어대학 도서관</t>
         </is>
       </c>
-      <c r="D273" s="2" t="inlineStr"/>
+      <c r="D273" s="3" t="n">
+        <v>247034</v>
+      </c>
       <c r="E273" s="2" t="inlineStr"/>
       <c r="F273" s="2" t="inlineStr">
         <is>
@@ -15975,6 +16909,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -15990,7 +16925,9 @@
           <t>영남이공대학교 도서관</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr"/>
+      <c r="D274" s="3" t="n">
+        <v>222013</v>
+      </c>
       <c r="E274" s="2" t="inlineStr"/>
       <c r="F274" s="2" t="inlineStr">
         <is>
@@ -16032,6 +16969,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -16047,7 +16985,9 @@
           <t>영진전문대학교 도서관</t>
         </is>
       </c>
-      <c r="D275" s="2" t="inlineStr"/>
+      <c r="D275" s="3" t="n">
+        <v>222014</v>
+      </c>
       <c r="E275" s="2" t="inlineStr"/>
       <c r="F275" s="2" t="inlineStr">
         <is>
@@ -16089,6 +17029,7 @@
           <t>[교육부고시 비고] 구)영진전문대학('18 6월 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -16104,7 +17045,9 @@
           <t>유한대학교 도서관</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr"/>
+      <c r="D276" s="3" t="n">
+        <v>241042</v>
+      </c>
       <c r="E276" s="2" t="inlineStr"/>
       <c r="F276" s="2" t="inlineStr">
         <is>
@@ -16146,6 +17089,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -16161,7 +17105,9 @@
           <t>인덕대학교 도서관</t>
         </is>
       </c>
-      <c r="D277" s="2" t="inlineStr"/>
+      <c r="D277" s="3" t="n">
+        <v>211049</v>
+      </c>
       <c r="E277" s="2" t="inlineStr"/>
       <c r="F277" s="2" t="inlineStr">
         <is>
@@ -16203,6 +17149,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -16218,7 +17165,9 @@
           <t>재능대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D278" s="2" t="inlineStr"/>
+      <c r="D278" s="3" t="n">
+        <v>228004</v>
+      </c>
       <c r="E278" s="2" t="inlineStr"/>
       <c r="F278" s="2" t="inlineStr">
         <is>
@@ -16261,6 +17210,7 @@
 구)인천재능대학교('24 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -16276,7 +17226,9 @@
           <t>장안대학교 도서관</t>
         </is>
       </c>
-      <c r="D279" s="2" t="inlineStr"/>
+      <c r="D279" s="3" t="n">
+        <v>241043</v>
+      </c>
       <c r="E279" s="2" t="inlineStr"/>
       <c r="F279" s="2" t="inlineStr">
         <is>
@@ -16318,6 +17270,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -16333,7 +17286,9 @@
           <t>전남과학대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D280" s="2" t="inlineStr"/>
+      <c r="D280" s="3" t="n">
+        <v>246011</v>
+      </c>
       <c r="E280" s="2" t="inlineStr"/>
       <c r="F280" s="2" t="inlineStr">
         <is>
@@ -16375,6 +17330,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -16390,7 +17346,9 @@
           <t>전북과학대학교 문헌정보관</t>
         </is>
       </c>
-      <c r="D281" s="2" t="inlineStr"/>
+      <c r="D281" s="3" t="n">
+        <v>245022</v>
+      </c>
       <c r="E281" s="2" t="inlineStr"/>
       <c r="F281" s="2" t="inlineStr">
         <is>
@@ -16432,6 +17390,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -16447,7 +17406,9 @@
           <t>전주비전대학교 도서관</t>
         </is>
       </c>
-      <c r="D282" s="2" t="inlineStr"/>
+      <c r="D282" s="3" t="n">
+        <v>245014</v>
+      </c>
       <c r="E282" s="2" t="inlineStr"/>
       <c r="F282" s="2" t="inlineStr">
         <is>
@@ -16489,6 +17450,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -16504,7 +17466,9 @@
           <t>제주관광대학교 도서관</t>
         </is>
       </c>
-      <c r="D283" s="2" t="inlineStr"/>
+      <c r="D283" s="3" t="n">
+        <v>249005</v>
+      </c>
       <c r="E283" s="2" t="inlineStr"/>
       <c r="F283" s="2" t="inlineStr">
         <is>
@@ -16546,6 +17510,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -16561,7 +17526,9 @@
           <t>조선이공대학교 도서관</t>
         </is>
       </c>
-      <c r="D284" s="2" t="inlineStr"/>
+      <c r="D284" s="3" t="n">
+        <v>224013</v>
+      </c>
       <c r="E284" s="2" t="inlineStr"/>
       <c r="F284" s="2" t="inlineStr">
         <is>
@@ -16603,6 +17570,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -16618,7 +17586,9 @@
           <t>충북도립대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D285" s="2" t="inlineStr"/>
+      <c r="D285" s="3" t="n">
+        <v>243018</v>
+      </c>
       <c r="E285" s="2" t="inlineStr"/>
       <c r="F285" s="2" t="inlineStr">
         <is>
@@ -16660,6 +17630,7 @@
           <t>[교육부고시 비고] 구)충북도립대학('19 1월 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -16675,7 +17646,9 @@
           <t>충북보건과학대학교 도서관</t>
         </is>
       </c>
-      <c r="D286" s="2" t="inlineStr"/>
+      <c r="D286" s="3" t="n">
+        <v>243028</v>
+      </c>
       <c r="E286" s="2" t="inlineStr"/>
       <c r="F286" s="2" t="inlineStr">
         <is>
@@ -16717,6 +17690,7 @@
           <t>[교육부고시 비고] 구)주성대학('12 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -16732,7 +17706,9 @@
           <t>충청대학교 도서관</t>
         </is>
       </c>
-      <c r="D287" s="2" t="inlineStr"/>
+      <c r="D287" s="3" t="n">
+        <v>243011</v>
+      </c>
       <c r="E287" s="2" t="inlineStr"/>
       <c r="F287" s="2" t="inlineStr">
         <is>
@@ -16774,6 +17750,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -16789,7 +17766,9 @@
           <t>한국관광대학교 도서관</t>
         </is>
       </c>
-      <c r="D288" s="2" t="inlineStr"/>
+      <c r="D288" s="3" t="n">
+        <v>241077</v>
+      </c>
       <c r="E288" s="2" t="inlineStr"/>
       <c r="F288" s="2" t="inlineStr">
         <is>
@@ -16831,6 +17810,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -16846,7 +17826,9 @@
           <t>한국승강기대학교 도서관</t>
         </is>
       </c>
-      <c r="D289" s="2" t="inlineStr"/>
+      <c r="D289" s="3" t="n">
+        <v>248034</v>
+      </c>
       <c r="E289" s="2" t="inlineStr"/>
       <c r="F289" s="2" t="inlineStr">
         <is>
@@ -16888,6 +17870,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -16903,7 +17886,9 @@
           <t>한국영상대학교 도서관</t>
         </is>
       </c>
-      <c r="D290" s="2" t="inlineStr"/>
+      <c r="D290" s="3" t="n">
+        <v>244025</v>
+      </c>
       <c r="E290" s="2" t="inlineStr"/>
       <c r="F290" s="2" t="inlineStr">
         <is>
@@ -16945,6 +17930,7 @@
           <t>[교육부고시 비고] 구)공주영상대학교('13 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -16960,7 +17946,9 @@
           <t>한양여자대학교 도서관</t>
         </is>
       </c>
-      <c r="D291" s="2" t="inlineStr"/>
+      <c r="D291" s="3" t="n">
+        <v>211063</v>
+      </c>
       <c r="E291" s="2" t="inlineStr"/>
       <c r="F291" s="2" t="inlineStr">
         <is>
@@ -17002,6 +17990,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -17017,7 +18006,9 @@
           <t>한영대학교 도서관</t>
         </is>
       </c>
-      <c r="D292" s="2" t="inlineStr"/>
+      <c r="D292" s="3" t="n">
+        <v>246028</v>
+      </c>
       <c r="E292" s="2" t="inlineStr"/>
       <c r="F292" s="2" t="inlineStr">
         <is>
@@ -17059,6 +18050,7 @@
           <t>[교육부고시 비고] 구)한영대학('19 하반기 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -17074,7 +18066,9 @@
           <t>호산대학교 도서관</t>
         </is>
       </c>
-      <c r="D293" s="2" t="inlineStr"/>
+      <c r="D293" s="3" t="n">
+        <v>247001</v>
+      </c>
       <c r="E293" s="2" t="inlineStr"/>
       <c r="F293" s="2" t="inlineStr">
         <is>
@@ -17116,6 +18110,7 @@
           <t>[교육부고시 비고] 구)경산1대학교('15 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -17131,7 +18126,9 @@
           <t>가톨릭상지대학교 도서관</t>
         </is>
       </c>
-      <c r="D294" s="2" t="inlineStr"/>
+      <c r="D294" s="3" t="n">
+        <v>247013</v>
+      </c>
       <c r="E294" s="2" t="inlineStr"/>
       <c r="F294" s="2" t="inlineStr">
         <is>
@@ -17173,6 +18170,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -17188,7 +18186,9 @@
           <t>강릉영동대학교 도서관</t>
         </is>
       </c>
-      <c r="D295" s="2" t="inlineStr"/>
+      <c r="D295" s="3" t="n">
+        <v>242010</v>
+      </c>
       <c r="E295" s="2" t="inlineStr"/>
       <c r="F295" s="2" t="inlineStr">
         <is>
@@ -17230,6 +18230,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -17245,7 +18246,9 @@
           <t>강원도립대학교 도서관</t>
         </is>
       </c>
-      <c r="D296" s="2" t="inlineStr"/>
+      <c r="D296" s="3" t="n">
+        <v>242020</v>
+      </c>
       <c r="E296" s="2" t="inlineStr"/>
       <c r="F296" s="2" t="inlineStr">
         <is>
@@ -17287,6 +18290,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -17302,7 +18306,9 @@
           <t>거제대학교 도서관</t>
         </is>
       </c>
-      <c r="D297" s="2" t="inlineStr"/>
+      <c r="D297" s="3" t="n">
+        <v>248001</v>
+      </c>
       <c r="E297" s="2" t="inlineStr"/>
       <c r="F297" s="2" t="inlineStr">
         <is>
@@ -17344,6 +18350,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -17359,7 +18366,9 @@
           <t>경남정보대학교 도서관</t>
         </is>
       </c>
-      <c r="D298" s="2" t="inlineStr"/>
+      <c r="D298" s="3" t="n">
+        <v>221001</v>
+      </c>
       <c r="E298" s="2" t="inlineStr"/>
       <c r="F298" s="2" t="inlineStr">
         <is>
@@ -17401,6 +18410,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -17416,7 +18426,9 @@
           <t>경민대학교 도서관</t>
         </is>
       </c>
-      <c r="D299" s="2" t="inlineStr"/>
+      <c r="D299" s="3" t="n">
+        <v>241003</v>
+      </c>
       <c r="E299" s="2" t="inlineStr"/>
       <c r="F299" s="2" t="inlineStr">
         <is>
@@ -17458,6 +18470,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -17473,7 +18486,9 @@
           <t>경복대학교 도서관</t>
         </is>
       </c>
-      <c r="D300" s="2" t="inlineStr"/>
+      <c r="D300" s="3" t="n">
+        <v>241004</v>
+      </c>
       <c r="E300" s="2" t="inlineStr"/>
       <c r="F300" s="2" t="inlineStr">
         <is>
@@ -17515,6 +18530,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -17530,7 +18546,9 @@
           <t>경북전문대학교 현암도서관</t>
         </is>
       </c>
-      <c r="D301" s="2" t="inlineStr"/>
+      <c r="D301" s="3" t="n">
+        <v>247003</v>
+      </c>
       <c r="E301" s="2" t="inlineStr"/>
       <c r="F301" s="2" t="inlineStr">
         <is>
@@ -17572,6 +18590,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -17587,7 +18606,9 @@
           <t>경인여자대학교 도서관</t>
         </is>
       </c>
-      <c r="D302" s="2" t="inlineStr"/>
+      <c r="D302" s="3" t="n">
+        <v>223002</v>
+      </c>
       <c r="E302" s="2" t="inlineStr"/>
       <c r="F302" s="2" t="inlineStr">
         <is>
@@ -17629,6 +18650,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -17644,7 +18666,9 @@
           <t>나주대학교 도서관</t>
         </is>
       </c>
-      <c r="D303" s="2" t="inlineStr"/>
+      <c r="D303" s="3" t="n">
+        <v>246018</v>
+      </c>
       <c r="E303" s="2" t="inlineStr"/>
       <c r="F303" s="2" t="inlineStr">
         <is>
@@ -17686,6 +18710,7 @@
           <t>[교육부고시 비고] 구)고구려대학교('24 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -17701,7 +18726,9 @@
           <t>광양보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D304" s="2" t="inlineStr"/>
+      <c r="D304" s="3" t="n">
+        <v>246012</v>
+      </c>
       <c r="E304" s="2" t="inlineStr"/>
       <c r="F304" s="2" t="inlineStr">
         <is>
@@ -17743,6 +18770,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -17758,7 +18786,9 @@
           <t>광주보건대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D305" s="2" t="inlineStr"/>
+      <c r="D305" s="3" t="n">
+        <v>224004</v>
+      </c>
       <c r="E305" s="2" t="inlineStr"/>
       <c r="F305" s="2" t="inlineStr">
         <is>
@@ -17800,6 +18830,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -17815,7 +18846,9 @@
           <t>군장대학교 도서관</t>
         </is>
       </c>
-      <c r="D306" s="2" t="inlineStr"/>
+      <c r="D306" s="3" t="n">
+        <v>245019</v>
+      </c>
       <c r="E306" s="2" t="inlineStr"/>
       <c r="F306" s="2" t="inlineStr">
         <is>
@@ -17857,6 +18890,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -17872,7 +18906,9 @@
           <t>김포대학교 도서관</t>
         </is>
       </c>
-      <c r="D307" s="2" t="inlineStr"/>
+      <c r="D307" s="3" t="n">
+        <v>241057</v>
+      </c>
       <c r="E307" s="2" t="inlineStr"/>
       <c r="F307" s="2" t="inlineStr">
         <is>
@@ -17914,6 +18950,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -17929,7 +18966,9 @@
           <t>김해대학교 도서관</t>
         </is>
       </c>
-      <c r="D308" s="2" t="inlineStr"/>
+      <c r="D308" s="3" t="n">
+        <v>248033</v>
+      </c>
       <c r="E308" s="2" t="inlineStr"/>
       <c r="F308" s="2" t="inlineStr">
         <is>
@@ -17971,6 +19010,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -17986,7 +19026,9 @@
           <t>농협대학교 도서관</t>
         </is>
       </c>
-      <c r="D309" s="2" t="inlineStr"/>
+      <c r="D309" s="3" t="n">
+        <v>241010</v>
+      </c>
       <c r="E309" s="2" t="inlineStr"/>
       <c r="F309" s="2" t="inlineStr">
         <is>
@@ -18028,6 +19070,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -18043,7 +19086,9 @@
           <t>대구보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D310" s="2" t="inlineStr"/>
+      <c r="D310" s="3" t="n">
+        <v>222010</v>
+      </c>
       <c r="E310" s="2" t="inlineStr"/>
       <c r="F310" s="2" t="inlineStr">
         <is>
@@ -18085,6 +19130,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -18100,7 +19146,9 @@
           <t>대림대학교 도서관</t>
         </is>
       </c>
-      <c r="D311" s="2" t="inlineStr"/>
+      <c r="D311" s="3" t="n">
+        <v>241011</v>
+      </c>
       <c r="E311" s="2" t="inlineStr"/>
       <c r="F311" s="2" t="inlineStr">
         <is>
@@ -18142,6 +19190,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N311" s="3" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -18157,7 +19206,9 @@
           <t>동남보건대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D312" s="2" t="inlineStr"/>
+      <c r="D312" s="3" t="n">
+        <v>241016</v>
+      </c>
       <c r="E312" s="2" t="inlineStr"/>
       <c r="F312" s="2" t="inlineStr">
         <is>
@@ -18199,6 +19250,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -18214,7 +19266,9 @@
           <t>동아방송예술대학교 도서관</t>
         </is>
       </c>
-      <c r="D313" s="2" t="inlineStr"/>
+      <c r="D313" s="3" t="n">
+        <v>241062</v>
+      </c>
       <c r="E313" s="2" t="inlineStr"/>
       <c r="F313" s="2" t="inlineStr">
         <is>
@@ -18256,6 +19310,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N313" s="3" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -18271,7 +19326,9 @@
           <t>동아보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D314" s="2" t="inlineStr"/>
+      <c r="D314" s="3" t="n">
+        <v>246015</v>
+      </c>
       <c r="E314" s="2" t="inlineStr"/>
       <c r="F314" s="2" t="inlineStr">
         <is>
@@ -18313,6 +19370,7 @@
           <t>[교육부고시 비고] 구)동아인재대학교('16 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -18328,7 +19386,9 @@
           <t>동양미래대학교 도서관</t>
         </is>
       </c>
-      <c r="D315" s="2" t="inlineStr"/>
+      <c r="D315" s="3" t="n">
+        <v>211022</v>
+      </c>
       <c r="E315" s="2" t="inlineStr"/>
       <c r="F315" s="2" t="inlineStr">
         <is>
@@ -18370,6 +19430,7 @@
           <t>[교육부고시 비고] 구)동양공업전문대학('12 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N315" s="3" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -18385,7 +19446,9 @@
           <t>동원대학교 도서관</t>
         </is>
       </c>
-      <c r="D316" s="2" t="inlineStr"/>
+      <c r="D316" s="3" t="n">
+        <v>241058</v>
+      </c>
       <c r="E316" s="2" t="inlineStr"/>
       <c r="F316" s="2" t="inlineStr">
         <is>
@@ -18427,6 +19490,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -18442,7 +19506,9 @@
           <t>부산보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D317" s="2" t="inlineStr"/>
+      <c r="D317" s="3" t="n">
+        <v>221011</v>
+      </c>
       <c r="E317" s="2" t="inlineStr"/>
       <c r="F317" s="2" t="inlineStr">
         <is>
@@ -18484,6 +19550,7 @@
           <t>[교육부고시 비고] 구)동주대학교('23.3.1 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N317" s="3" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -18499,7 +19566,9 @@
           <t>마산대학교 도서관</t>
         </is>
       </c>
-      <c r="D318" s="2" t="inlineStr"/>
+      <c r="D318" s="3" t="n">
+        <v>248005</v>
+      </c>
       <c r="E318" s="2" t="inlineStr"/>
       <c r="F318" s="2" t="inlineStr">
         <is>
@@ -18541,6 +19610,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -18556,7 +19626,9 @@
           <t>명지전문대학 도서관</t>
         </is>
       </c>
-      <c r="D319" s="2" t="inlineStr"/>
+      <c r="D319" s="3" t="n">
+        <v>211024</v>
+      </c>
       <c r="E319" s="2" t="inlineStr"/>
       <c r="F319" s="2" t="inlineStr">
         <is>
@@ -18598,6 +19670,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N319" s="3" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -18613,7 +19686,9 @@
           <t>목포과학대학교 도서관</t>
         </is>
       </c>
-      <c r="D320" s="2" t="inlineStr"/>
+      <c r="D320" s="3" t="n">
+        <v>246003</v>
+      </c>
       <c r="E320" s="2" t="inlineStr"/>
       <c r="F320" s="2" t="inlineStr">
         <is>
@@ -18655,6 +19730,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -18670,7 +19746,9 @@
           <t>배화여자대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D321" s="2" t="inlineStr"/>
+      <c r="D321" s="3" t="n">
+        <v>211025</v>
+      </c>
       <c r="E321" s="2" t="inlineStr"/>
       <c r="F321" s="2" t="inlineStr">
         <is>
@@ -18712,6 +19790,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N321" s="3" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -18727,7 +19806,9 @@
           <t>삼육보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D322" s="2" t="inlineStr"/>
+      <c r="D322" s="3" t="n">
+        <v>211026</v>
+      </c>
       <c r="E322" s="2" t="inlineStr"/>
       <c r="F322" s="2" t="inlineStr">
         <is>
@@ -18769,6 +19850,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -18784,7 +19866,9 @@
           <t>서영대학교 도서관</t>
         </is>
       </c>
-      <c r="D323" s="2" t="inlineStr"/>
+      <c r="D323" s="3" t="n">
+        <v>224008</v>
+      </c>
       <c r="E323" s="2" t="inlineStr"/>
       <c r="F323" s="2" t="inlineStr">
         <is>
@@ -18826,6 +19910,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -18841,7 +19926,9 @@
           <t>서울예술대학교 예술정보센터</t>
         </is>
       </c>
-      <c r="D324" s="2" t="inlineStr"/>
+      <c r="D324" s="3" t="n">
+        <v>211037</v>
+      </c>
       <c r="E324" s="2" t="inlineStr"/>
       <c r="F324" s="2" t="inlineStr">
         <is>
@@ -18883,6 +19970,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -18898,7 +19986,9 @@
           <t>서정대학교 중앙도서관</t>
         </is>
       </c>
-      <c r="D325" s="2" t="inlineStr"/>
+      <c r="D325" s="3" t="n">
+        <v>241086</v>
+      </c>
       <c r="E325" s="2" t="inlineStr"/>
       <c r="F325" s="2" t="inlineStr">
         <is>
@@ -18940,6 +20030,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -18955,7 +20046,9 @@
           <t>선린대학교 도서관</t>
         </is>
       </c>
-      <c r="D326" s="2" t="inlineStr"/>
+      <c r="D326" s="3" t="n">
+        <v>247014</v>
+      </c>
       <c r="E326" s="2" t="inlineStr"/>
       <c r="F326" s="2" t="inlineStr">
         <is>
@@ -18997,6 +20090,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -19012,7 +20106,9 @@
           <t>성운대학교 학술정보센터</t>
         </is>
       </c>
-      <c r="D327" s="2" t="inlineStr"/>
+      <c r="D327" s="3" t="n">
+        <v>247035</v>
+      </c>
       <c r="E327" s="2" t="inlineStr"/>
       <c r="F327" s="2" t="inlineStr">
         <is>
@@ -19054,6 +20150,7 @@
           <t>[교육부고시 비고] 구)성덕대학교('20 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -19069,7 +20166,9 @@
           <t>수성대학교 도서관</t>
         </is>
       </c>
-      <c r="D328" s="2" t="inlineStr"/>
+      <c r="D328" s="3" t="n">
+        <v>227009</v>
+      </c>
       <c r="E328" s="2" t="inlineStr"/>
       <c r="F328" s="2" t="inlineStr">
         <is>
@@ -19111,6 +20210,7 @@
           <t>[교육부고시 비고] 구)대구산업정보대학('12 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -19126,7 +20226,9 @@
           <t>수원과학대학교 도서관</t>
         </is>
       </c>
-      <c r="D329" s="2" t="inlineStr"/>
+      <c r="D329" s="3" t="n">
+        <v>241033</v>
+      </c>
       <c r="E329" s="2" t="inlineStr"/>
       <c r="F329" s="2" t="inlineStr">
         <is>
@@ -19168,6 +20270,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -19183,7 +20286,9 @@
           <t>신성대학교 도서관</t>
         </is>
       </c>
-      <c r="D330" s="2" t="inlineStr"/>
+      <c r="D330" s="3" t="n">
+        <v>244027</v>
+      </c>
       <c r="E330" s="2" t="inlineStr"/>
       <c r="F330" s="2" t="inlineStr">
         <is>
@@ -19225,6 +20330,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -19240,7 +20346,9 @@
           <t>안동과학대학교 도서관</t>
         </is>
       </c>
-      <c r="D331" s="2" t="inlineStr"/>
+      <c r="D331" s="3" t="n">
+        <v>247016</v>
+      </c>
       <c r="E331" s="2" t="inlineStr"/>
       <c r="F331" s="2" t="inlineStr">
         <is>
@@ -19282,6 +20390,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -19297,7 +20406,9 @@
           <t>안산대학교 도서관</t>
         </is>
       </c>
-      <c r="D332" s="2" t="inlineStr"/>
+      <c r="D332" s="3" t="n">
+        <v>241061</v>
+      </c>
       <c r="E332" s="2" t="inlineStr"/>
       <c r="F332" s="2" t="inlineStr">
         <is>
@@ -19339,6 +20450,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -19354,7 +20466,9 @@
           <t>연성대학교 연곡도서관</t>
         </is>
       </c>
-      <c r="D333" s="2" t="inlineStr"/>
+      <c r="D333" s="3" t="n">
+        <v>241040</v>
+      </c>
       <c r="E333" s="2" t="inlineStr"/>
       <c r="F333" s="2" t="inlineStr">
         <is>
@@ -19396,6 +20510,7 @@
           <t>[교육부고시 비고] 구)안양과학대학('12 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -19411,7 +20526,9 @@
           <t>연암공과대학교 도서관</t>
         </is>
       </c>
-      <c r="D334" s="2" t="inlineStr"/>
+      <c r="D334" s="3" t="n">
+        <v>248008</v>
+      </c>
       <c r="E334" s="2" t="inlineStr"/>
       <c r="F334" s="2" t="inlineStr">
         <is>
@@ -19453,6 +20570,7 @@
           <t>[교육부고시 비고] 구)연암공업대학('16 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -19468,7 +20586,9 @@
           <t>오산대학교 도서관</t>
         </is>
       </c>
-      <c r="D335" s="2" t="inlineStr"/>
+      <c r="D335" s="3" t="n">
+        <v>241041</v>
+      </c>
       <c r="E335" s="2" t="inlineStr"/>
       <c r="F335" s="2" t="inlineStr">
         <is>
@@ -19510,6 +20630,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -19525,7 +20646,9 @@
           <t>용인예술과학대학교 도서관</t>
         </is>
       </c>
-      <c r="D336" s="2" t="inlineStr"/>
+      <c r="D336" s="3" t="n">
+        <v>241056</v>
+      </c>
       <c r="E336" s="2" t="inlineStr"/>
       <c r="F336" s="2" t="inlineStr">
         <is>
@@ -19567,6 +20690,7 @@
           <t>[교육부고시 비고] 구)용인송담대학교('21 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -19582,7 +20706,9 @@
           <t>우송정보대학 우송도서관</t>
         </is>
       </c>
-      <c r="D337" s="2" t="inlineStr"/>
+      <c r="D337" s="3" t="n">
+        <v>225004</v>
+      </c>
       <c r="E337" s="2" t="inlineStr"/>
       <c r="F337" s="2" t="inlineStr">
         <is>
@@ -19624,6 +20750,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -19639,7 +20766,9 @@
           <t>울산과학대학교 도서관</t>
         </is>
       </c>
-      <c r="D338" s="2" t="inlineStr"/>
+      <c r="D338" s="3" t="n">
+        <v>248010</v>
+      </c>
       <c r="E338" s="2" t="inlineStr"/>
       <c r="F338" s="2" t="inlineStr">
         <is>
@@ -19681,6 +20810,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -19745,7 +20875,9 @@
           <t>인하공업전문대학 도서관</t>
         </is>
       </c>
-      <c r="D340" s="2" t="inlineStr"/>
+      <c r="D340" s="3" t="n">
+        <v>223008</v>
+      </c>
       <c r="E340" s="2" t="inlineStr"/>
       <c r="F340" s="2" t="inlineStr">
         <is>
@@ -19787,6 +20919,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -19802,7 +20935,9 @@
           <t>전주기전대학 도서관</t>
         </is>
       </c>
-      <c r="D341" s="2" t="inlineStr"/>
+      <c r="D341" s="3" t="n">
+        <v>245004</v>
+      </c>
       <c r="E341" s="2" t="inlineStr"/>
       <c r="F341" s="2" t="inlineStr">
         <is>
@@ -19844,6 +20979,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -19859,7 +20995,9 @@
           <t>제주한라대학교 도서관</t>
         </is>
       </c>
-      <c r="D342" s="2" t="inlineStr"/>
+      <c r="D342" s="3" t="n">
+        <v>249004</v>
+      </c>
       <c r="E342" s="2" t="inlineStr"/>
       <c r="F342" s="2" t="inlineStr">
         <is>
@@ -19901,6 +21039,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -19916,7 +21055,9 @@
           <t>진주보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D343" s="2" t="inlineStr"/>
+      <c r="D343" s="3" t="n">
+        <v>248013</v>
+      </c>
       <c r="E343" s="2" t="inlineStr"/>
       <c r="F343" s="2" t="inlineStr">
         <is>
@@ -19958,6 +21099,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -19973,7 +21115,9 @@
           <t>창원문성대학교 도서관</t>
         </is>
       </c>
-      <c r="D344" s="2" t="inlineStr"/>
+      <c r="D344" s="3" t="n">
+        <v>248020</v>
+      </c>
       <c r="E344" s="2" t="inlineStr"/>
       <c r="F344" s="2" t="inlineStr">
         <is>
@@ -20015,6 +21159,7 @@
           <t>[교육부고시 비고] 구)창원전문대학('11 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -20030,7 +21175,9 @@
           <t>청강문화산업대학교 도서관</t>
         </is>
       </c>
-      <c r="D345" s="2" t="inlineStr"/>
+      <c r="D345" s="3" t="n">
+        <v>241060</v>
+      </c>
       <c r="E345" s="2" t="inlineStr"/>
       <c r="F345" s="2" t="inlineStr">
         <is>
@@ -20072,6 +21219,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -20087,7 +21235,9 @@
           <t>청암대학교 학술정보센터</t>
         </is>
       </c>
-      <c r="D346" s="2" t="inlineStr"/>
+      <c r="D346" s="3" t="n">
+        <v>246006</v>
+      </c>
       <c r="E346" s="2" t="inlineStr"/>
       <c r="F346" s="2" t="inlineStr">
         <is>
@@ -20129,6 +21279,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -20144,7 +21295,9 @@
           <t>춘해보건대학교 도서관</t>
         </is>
       </c>
-      <c r="D347" s="2" t="inlineStr"/>
+      <c r="D347" s="3" t="n">
+        <v>221027</v>
+      </c>
       <c r="E347" s="2" t="inlineStr"/>
       <c r="F347" s="2" t="inlineStr">
         <is>
@@ -20186,6 +21339,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -20201,7 +21355,9 @@
           <t>충남도립대학교 도서관</t>
         </is>
       </c>
-      <c r="D348" s="2" t="inlineStr"/>
+      <c r="D348" s="3" t="n">
+        <v>244030</v>
+      </c>
       <c r="E348" s="2" t="inlineStr"/>
       <c r="F348" s="2" t="inlineStr">
         <is>
@@ -20243,6 +21399,7 @@
           <t>[교육부고시 비고] 구)충남도립청양대학('15 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -20258,7 +21415,9 @@
           <t>포항대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D349" s="2" t="inlineStr"/>
+      <c r="D349" s="3" t="n">
+        <v>247021</v>
+      </c>
       <c r="E349" s="2" t="inlineStr"/>
       <c r="F349" s="2" t="inlineStr">
         <is>
@@ -20300,6 +21459,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -20315,7 +21475,9 @@
           <t>한국골프과학기술대학교 도서관</t>
         </is>
       </c>
-      <c r="D350" s="2" t="inlineStr"/>
+      <c r="D350" s="3" t="n">
+        <v>242027</v>
+      </c>
       <c r="E350" s="2" t="inlineStr"/>
       <c r="F350" s="2" t="inlineStr">
         <is>
@@ -20357,6 +21519,7 @@
           <t>[교육부고시 비고] 구)한국골프대학교('24.9.1.변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -20372,7 +21535,9 @@
           <t>한국농수산대학교 도서관</t>
         </is>
       </c>
-      <c r="D351" s="2" t="inlineStr"/>
+      <c r="D351" s="3" t="n">
+        <v>241067</v>
+      </c>
       <c r="E351" s="2" t="inlineStr"/>
       <c r="F351" s="2" t="inlineStr">
         <is>
@@ -20414,6 +21579,7 @@
           <t>[교육부고시 비고] 구)한국농수산대학(22.6.1) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -20429,7 +21595,9 @@
           <t>한림성심대학교 한빛도서관</t>
         </is>
       </c>
-      <c r="D352" s="2" t="inlineStr"/>
+      <c r="D352" s="3" t="n">
+        <v>242013</v>
+      </c>
       <c r="E352" s="2" t="inlineStr"/>
       <c r="F352" s="2" t="inlineStr">
         <is>
@@ -20471,6 +21639,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -20486,7 +21655,9 @@
           <t>혜전대학교 도서관</t>
         </is>
       </c>
-      <c r="D353" s="2" t="inlineStr"/>
+      <c r="D353" s="3" t="n">
+        <v>244017</v>
+      </c>
       <c r="E353" s="2" t="inlineStr"/>
       <c r="F353" s="2" t="inlineStr">
         <is>
@@ -20528,6 +21699,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -20543,7 +21715,9 @@
           <t>군산간호대학교 도서관</t>
         </is>
       </c>
-      <c r="D354" s="2" t="inlineStr"/>
+      <c r="D354" s="3" t="n">
+        <v>245001</v>
+      </c>
       <c r="E354" s="2" t="inlineStr"/>
       <c r="F354" s="2" t="inlineStr">
         <is>
@@ -20585,6 +21759,7 @@
           <t>[교육부고시 비고] 3년제→4년제('17) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -20600,7 +21775,9 @@
           <t>기독간호대학교 도서관</t>
         </is>
       </c>
-      <c r="D355" s="2" t="inlineStr"/>
+      <c r="D355" s="3" t="n">
+        <v>224006</v>
+      </c>
       <c r="E355" s="2" t="inlineStr"/>
       <c r="F355" s="2" t="inlineStr">
         <is>
@@ -20642,6 +21819,7 @@
           <t>[교육부고시 비고] 3년제→4년제('17) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -20657,7 +21835,9 @@
           <t>서울여자간호대학교 도서관</t>
         </is>
       </c>
-      <c r="D356" s="2" t="inlineStr"/>
+      <c r="D356" s="3" t="n">
+        <v>211030</v>
+      </c>
       <c r="E356" s="2" t="inlineStr"/>
       <c r="F356" s="2" t="inlineStr">
         <is>
@@ -20699,6 +21879,7 @@
           <t>[교육부고시 비고] 3년제→4년제('17) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -20714,7 +21895,9 @@
           <t>조선간호대학교 도서관</t>
         </is>
       </c>
-      <c r="D357" s="2" t="inlineStr"/>
+      <c r="D357" s="3" t="n">
+        <v>224012</v>
+      </c>
       <c r="E357" s="2" t="inlineStr"/>
       <c r="F357" s="2" t="inlineStr">
         <is>
@@ -20756,6 +21939,7 @@
           <t>[교육부고시 비고] 3년제→4년제('17) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -20820,7 +22004,9 @@
           <t>한국복지사이버대학교 도서관</t>
         </is>
       </c>
-      <c r="D359" s="2" t="inlineStr"/>
+      <c r="D359" s="3" t="n">
+        <v>247043</v>
+      </c>
       <c r="E359" s="2" t="inlineStr"/>
       <c r="F359" s="2" t="inlineStr">
         <is>
@@ -20862,6 +22048,7 @@
           <t>[교육부고시 비고] 구)한국복지사이버대학('24.5.1 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -20877,7 +22064,9 @@
           <t>한국학대학원 도서관</t>
         </is>
       </c>
-      <c r="D360" s="2" t="inlineStr"/>
+      <c r="D360" s="3" t="n">
+        <v>341054</v>
+      </c>
       <c r="E360" s="2" t="inlineStr"/>
       <c r="F360" s="2" t="inlineStr">
         <is>
@@ -20919,6 +22108,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -20934,7 +22124,9 @@
           <t>개신대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D361" s="2" t="inlineStr"/>
+      <c r="D361" s="3" t="n">
+        <v>211094</v>
+      </c>
       <c r="E361" s="2" t="inlineStr"/>
       <c r="F361" s="2" t="inlineStr">
         <is>
@@ -20976,6 +22168,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -20991,7 +22184,9 @@
           <t>건신대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D362" s="2" t="inlineStr"/>
+      <c r="D362" s="3" t="n">
+        <v>225022</v>
+      </c>
       <c r="E362" s="2" t="inlineStr"/>
       <c r="F362" s="2" t="inlineStr">
         <is>
@@ -21033,6 +22228,7 @@
           <t>[교육부고시 비고] 구)복음신학대학원대학교('15 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -21097,7 +22293,9 @@
           <t>과학기술연합대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D364" s="2" t="inlineStr"/>
+      <c r="D364" s="3" t="n">
+        <v>230003</v>
+      </c>
       <c r="E364" s="2" t="inlineStr"/>
       <c r="F364" s="2" t="inlineStr">
         <is>
@@ -21139,6 +22337,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -21154,7 +22353,9 @@
           <t>국립암센터국제암대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D365" s="2" t="inlineStr"/>
+      <c r="D365" s="3" t="n">
+        <v>341197</v>
+      </c>
       <c r="E365" s="2" t="inlineStr"/>
       <c r="F365" s="2" t="inlineStr">
         <is>
@@ -21196,6 +22397,7 @@
           <t>[교육부고시 비고] 2014년 개교, 구)국제암대학원대학교('17 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -21211,7 +22413,9 @@
           <t>국제뇌교육종합대학원대학교 성재관</t>
         </is>
       </c>
-      <c r="D366" s="2" t="inlineStr"/>
+      <c r="D366" s="3" t="n">
+        <v>244039</v>
+      </c>
       <c r="E366" s="2" t="inlineStr"/>
       <c r="F366" s="2" t="inlineStr">
         <is>
@@ -21253,6 +22457,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
@@ -21317,7 +22522,9 @@
           <t>수도국제대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D368" s="2" t="inlineStr"/>
+      <c r="D368" s="3" t="n">
+        <v>211081</v>
+      </c>
       <c r="E368" s="2" t="inlineStr"/>
       <c r="F368" s="2" t="inlineStr">
         <is>
@@ -21359,6 +22566,7 @@
           <t>[교육부고시 비고] 구)국제신학대학원대학교('22.9.1 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
@@ -21374,7 +22582,9 @@
           <t>국제언어대학원대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D369" s="2" t="inlineStr"/>
+      <c r="D369" s="3" t="n">
+        <v>211135</v>
+      </c>
       <c r="E369" s="2" t="inlineStr"/>
       <c r="F369" s="2" t="inlineStr">
         <is>
@@ -21416,6 +22626,7 @@
           <t>[교육부고시 비고] 구)국제영어대학원대학교('23.9 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N369" s="3" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
@@ -21480,7 +22691,9 @@
           <t>대한신학대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D371" s="2" t="inlineStr"/>
+      <c r="D371" s="3" t="n">
+        <v>241068</v>
+      </c>
       <c r="E371" s="2" t="inlineStr"/>
       <c r="F371" s="2" t="inlineStr">
         <is>
@@ -21522,6 +22735,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N371" s="3" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
@@ -21537,7 +22751,9 @@
           <t>동방문화대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D372" s="2" t="inlineStr"/>
+      <c r="D372" s="3" t="n">
+        <v>211101</v>
+      </c>
       <c r="E372" s="2" t="inlineStr"/>
       <c r="F372" s="2" t="inlineStr">
         <is>
@@ -21579,6 +22795,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
@@ -21594,7 +22811,9 @@
           <t>베뢰아국제대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D373" s="2" t="inlineStr"/>
+      <c r="D373" s="3" t="n">
+        <v>211077</v>
+      </c>
       <c r="E373" s="2" t="inlineStr"/>
       <c r="F373" s="2" t="inlineStr">
         <is>
@@ -21636,6 +22855,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N373" s="3" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
@@ -21700,7 +22920,9 @@
           <t>서울과학종합대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D375" s="2" t="inlineStr"/>
+      <c r="D375" s="3" t="n">
+        <v>211141</v>
+      </c>
       <c r="E375" s="2" t="inlineStr"/>
       <c r="F375" s="2" t="inlineStr">
         <is>
@@ -21742,6 +22964,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N375" s="3" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
@@ -21757,7 +22980,9 @@
           <t>서울벤처대학원대학교 학술정보관</t>
         </is>
       </c>
-      <c r="D376" s="2" t="inlineStr"/>
+      <c r="D376" s="3" t="n">
+        <v>211105</v>
+      </c>
       <c r="E376" s="2" t="inlineStr"/>
       <c r="F376" s="2" t="inlineStr">
         <is>
@@ -21799,6 +23024,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
@@ -21814,7 +23040,9 @@
           <t>서울불교대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D377" s="2" t="inlineStr"/>
+      <c r="D377" s="3" t="n">
+        <v>211096</v>
+      </c>
       <c r="E377" s="2" t="inlineStr"/>
       <c r="F377" s="2" t="inlineStr">
         <is>
@@ -21856,6 +23084,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N377" s="3" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
@@ -21871,7 +23100,9 @@
           <t>서울상담심리대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D378" s="2" t="inlineStr"/>
+      <c r="D378" s="3" t="n">
+        <v>211113</v>
+      </c>
       <c r="E378" s="2" t="inlineStr"/>
       <c r="F378" s="2" t="inlineStr">
         <is>
@@ -21913,6 +23144,7 @@
           <t>[교육부고시 비고] 구)용문상담심리대학원대학교('21.9.1 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
@@ -21928,7 +23160,9 @@
           <t>서울성경신학대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D379" s="2" t="inlineStr"/>
+      <c r="D379" s="3" t="n">
+        <v>211082</v>
+      </c>
       <c r="E379" s="2" t="inlineStr"/>
       <c r="F379" s="2" t="inlineStr">
         <is>
@@ -21970,6 +23204,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
@@ -22042,7 +23277,9 @@
           <t>선학유피대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D381" s="2" t="inlineStr"/>
+      <c r="D381" s="3" t="n">
+        <v>241079</v>
+      </c>
       <c r="E381" s="2" t="inlineStr"/>
       <c r="F381" s="2" t="inlineStr">
         <is>
@@ -22084,6 +23321,7 @@
           <t>[교육부고시 비고] 구)청심신학대학원대학교('16.9 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
@@ -22099,7 +23337,9 @@
           <t>성산효대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D382" s="2" t="inlineStr"/>
+      <c r="D382" s="3" t="n">
+        <v>223013</v>
+      </c>
       <c r="E382" s="2" t="inlineStr"/>
       <c r="F382" s="2" t="inlineStr">
         <is>
@@ -22141,6 +23381,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
@@ -22156,7 +23397,9 @@
           <t>성서침례대학원대학교 초헌도서관</t>
         </is>
       </c>
-      <c r="D383" s="2" t="inlineStr"/>
+      <c r="D383" s="3" t="n">
+        <v>241084</v>
+      </c>
       <c r="E383" s="2" t="inlineStr"/>
       <c r="F383" s="2" t="inlineStr">
         <is>
@@ -22198,6 +23441,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N383" s="3" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
@@ -22213,7 +23457,9 @@
           <t>순복음대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D384" s="2" t="inlineStr"/>
+      <c r="D384" s="3" t="n">
+        <v>211098</v>
+      </c>
       <c r="E384" s="2" t="inlineStr"/>
       <c r="F384" s="2" t="inlineStr">
         <is>
@@ -22255,6 +23501,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
@@ -22270,7 +23517,9 @@
           <t>실천신학대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D385" s="2" t="inlineStr"/>
+      <c r="D385" s="3" t="n">
+        <v>241088</v>
+      </c>
       <c r="E385" s="2" t="inlineStr"/>
       <c r="F385" s="2" t="inlineStr">
         <is>
@@ -22312,6 +23561,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N385" s="3" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
@@ -22327,7 +23577,9 @@
           <t>에스라성경대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D386" s="2" t="inlineStr"/>
+      <c r="D386" s="3" t="n">
+        <v>241082</v>
+      </c>
       <c r="E386" s="2" t="inlineStr"/>
       <c r="F386" s="2" t="inlineStr">
         <is>
@@ -22369,6 +23621,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
@@ -22384,7 +23637,9 @@
           <t>예명대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D387" s="2" t="inlineStr"/>
+      <c r="D387" s="3" t="n">
+        <v>211136</v>
+      </c>
       <c r="E387" s="2" t="inlineStr"/>
       <c r="F387" s="2" t="inlineStr">
         <is>
@@ -22426,6 +23681,7 @@
           <t>[교육부고시 비고] 구)예일신학대학원대학교('15 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N387" s="3" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
@@ -22441,7 +23697,9 @@
           <t>온석대학원대학교 학술정보원</t>
         </is>
       </c>
-      <c r="D388" s="2" t="inlineStr"/>
+      <c r="D388" s="3" t="n">
+        <v>241107</v>
+      </c>
       <c r="E388" s="2" t="inlineStr"/>
       <c r="F388" s="2" t="inlineStr">
         <is>
@@ -22483,6 +23741,7 @@
           <t>[교육부고시 비고] 구)중앙신학대학원대학교('19 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
@@ -22498,7 +23757,9 @@
           <t>원불교대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D389" s="2" t="inlineStr"/>
+      <c r="D389" s="3" t="n">
+        <v>245023</v>
+      </c>
       <c r="E389" s="2" t="inlineStr"/>
       <c r="F389" s="2" t="inlineStr">
         <is>
@@ -22540,6 +23801,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N389" s="3" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
@@ -22555,7 +23817,9 @@
           <t>웨스트민스터신학대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D390" s="2" t="inlineStr"/>
+      <c r="D390" s="3" t="n">
+        <v>211078</v>
+      </c>
       <c r="E390" s="2" t="inlineStr"/>
       <c r="F390" s="2" t="inlineStr">
         <is>
@@ -22597,6 +23861,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
@@ -22612,7 +23877,9 @@
           <t>제네바신학대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D391" s="2" t="inlineStr"/>
+      <c r="D391" s="3" t="n">
+        <v>241066</v>
+      </c>
       <c r="E391" s="2" t="inlineStr"/>
       <c r="F391" s="2" t="inlineStr">
         <is>
@@ -22654,6 +23921,7 @@
           <t>[교육부고시 비고] 2011년 개교, 2013년 공시시작, 구)서울제일대학원대학교 / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N391" s="3" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
@@ -22669,7 +23937,9 @@
           <t>주안대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D392" s="2" t="inlineStr"/>
+      <c r="D392" s="3" t="n">
+        <v>228003</v>
+      </c>
       <c r="E392" s="2" t="inlineStr"/>
       <c r="F392" s="2" t="inlineStr">
         <is>
@@ -22711,6 +23981,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -22726,7 +23997,9 @@
           <t>치유상담대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D393" s="2" t="inlineStr"/>
+      <c r="D393" s="3" t="n">
+        <v>211121</v>
+      </c>
       <c r="E393" s="2" t="inlineStr"/>
       <c r="F393" s="2" t="inlineStr">
         <is>
@@ -22768,6 +24041,7 @@
           <t>[교육부고시 비고] 2015년 개교, 구)크리스찬치유상담대학원대학교('17 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N393" s="3" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -22783,7 +24057,9 @@
           <t>한국개발연구원국제정책대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D394" s="2" t="inlineStr"/>
+      <c r="D394" s="3" t="n">
+        <v>211076</v>
+      </c>
       <c r="E394" s="2" t="inlineStr"/>
       <c r="F394" s="2" t="inlineStr">
         <is>
@@ -22825,6 +24101,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
@@ -22840,7 +24117,9 @@
           <t>한국상담대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D395" s="2" t="inlineStr"/>
+      <c r="D395" s="3" t="n">
+        <v>211117</v>
+      </c>
       <c r="E395" s="2" t="inlineStr"/>
       <c r="F395" s="2" t="inlineStr">
         <is>
@@ -22882,6 +24161,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N395" s="3" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
@@ -22897,7 +24177,9 @@
           <t>한국전력국제원자력대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D396" s="2" t="inlineStr"/>
+      <c r="D396" s="3" t="n">
+        <v>231002</v>
+      </c>
       <c r="E396" s="2" t="inlineStr"/>
       <c r="F396" s="2" t="inlineStr">
         <is>
@@ -22939,6 +24221,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -22954,7 +24237,9 @@
           <t>합동신학대학원대학교 변화산 기념 도서관</t>
         </is>
       </c>
-      <c r="D397" s="2" t="inlineStr"/>
+      <c r="D397" s="3" t="n">
+        <v>241051</v>
+      </c>
       <c r="E397" s="2" t="inlineStr"/>
       <c r="F397" s="2" t="inlineStr">
         <is>
@@ -22996,6 +24281,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N397" s="3" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -23011,7 +24297,9 @@
           <t>횃불트리니티신학대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D398" s="2" t="inlineStr"/>
+      <c r="D398" s="3" t="n">
+        <v>211075</v>
+      </c>
       <c r="E398" s="2" t="inlineStr"/>
       <c r="F398" s="2" t="inlineStr">
         <is>
@@ -23053,6 +24341,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -23068,7 +24357,9 @@
           <t>구세군사관대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D399" s="2" t="inlineStr"/>
+      <c r="D399" s="3" t="n">
+        <v>241009</v>
+      </c>
       <c r="E399" s="2" t="inlineStr"/>
       <c r="F399" s="2" t="inlineStr">
         <is>
@@ -23110,6 +24401,7 @@
           <t>[교육부고시 비고] 구)구세군사관학교(전문→대학원대학)('15) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N399" s="3" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -23125,7 +24417,9 @@
           <t>서울미디어대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D400" s="2" t="inlineStr"/>
+      <c r="D400" s="3" t="n">
+        <v>211140</v>
+      </c>
       <c r="E400" s="2" t="inlineStr"/>
       <c r="F400" s="2" t="inlineStr">
         <is>
@@ -23167,6 +24461,7 @@
           <t>[교육부고시 비고] 구)한독미디어대학원대학교('16 변경) / 장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
@@ -23182,7 +24477,9 @@
           <t>서울사회복지대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D401" s="2" t="inlineStr"/>
+      <c r="D401" s="3" t="n">
+        <v>211137</v>
+      </c>
       <c r="E401" s="2" t="inlineStr"/>
       <c r="F401" s="2" t="inlineStr">
         <is>
@@ -23224,6 +24521,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N401" s="3" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -23239,7 +24537,9 @@
           <t>한림국제대학원대학교 문헌정보실</t>
         </is>
       </c>
-      <c r="D402" s="2" t="inlineStr"/>
+      <c r="D402" s="3" t="n">
+        <v>211109</v>
+      </c>
       <c r="E402" s="2" t="inlineStr"/>
       <c r="F402" s="2" t="inlineStr">
         <is>
@@ -23281,6 +24581,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
@@ -23296,7 +24597,9 @@
           <t>한반도국제대학원대학교 도서관</t>
         </is>
       </c>
-      <c r="D403" s="2" t="inlineStr"/>
+      <c r="D403" s="3" t="n">
+        <v>211102</v>
+      </c>
       <c r="E403" s="2" t="inlineStr"/>
       <c r="F403" s="2" t="inlineStr">
         <is>
@@ -23338,6 +24641,7 @@
           <t>장애학생지원센터 통계: 조사대상 아님(전문대학·대학원대학 등)</t>
         </is>
       </c>
+      <c r="N403" s="3" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
@@ -23353,7 +24657,9 @@
           <t>태재대학교 디지털도서관</t>
         </is>
       </c>
-      <c r="D404" s="2" t="inlineStr"/>
+      <c r="D404" s="3" t="n">
+        <v>211142</v>
+      </c>
       <c r="E404" s="2" t="inlineStr"/>
       <c r="F404" s="2" t="inlineStr">
         <is>
@@ -23395,6 +24701,7 @@
           <t>[교육부고시 비고] 23.9.1 / 장애학생지원센터 통계: 없음(X)</t>
         </is>
       </c>
+      <c r="N404" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23446,7 +24753,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>업로드하신 3개 원본 파일(교육부 고시, KERIS 대학도서관 통계, 장애학생지원센터 현황)에 해당 항목이 없어 공란으로 두었습니다. 국립중앙도서관 도서관코드 조회 결과를 주시면 채워 넣겠습니다.</t>
+          <t>국립중앙도서관 도서관코드 조회 결과를 반영해 도서관부호(D열)를 채웠습니다. 캠퍼스 도서관이 여러 개로 통합된 학교(35개교)는 대표 캠퍼스 1개의 부호만 D열에 넣고, 나머지 캠퍼스 도서관명과 부호는 N열(통합도서관부호)에 "도서관명: 부호" 형식으로 나열했습니다. KERIS 통계 자체가 없던 학교(16개교) 등 부호를 확인하지 못한 경우는 공란으로 두었습니다. 주소는 이번 작업 범위가 아니어서 공란으로 유지했습니다.</t>
         </is>
       </c>
     </row>
